--- a/output/crm_with_outreach.xlsx
+++ b/output/crm_with_outreach.xlsx
@@ -13,8 +13,8 @@
     <sheet name="Channel &amp; CRM Summary" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cleaned Dataset'!$A$2:$AQ$166</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Disqualified Leads'!$A$1:$AK$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cleaned Dataset'!$A$2:$AR$166</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Disqualified Leads'!$A$1:$AL$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,6 +42,9 @@
     <font>
       <b val="1"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -76,7 +79,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -95,6 +98,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -460,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ166"/>
+  <dimension ref="A1:AR166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -501,11 +505,12 @@
     <col width="22" customWidth="1" min="36" max="36"/>
     <col width="19" customWidth="1" min="37" max="37"/>
     <col width="12" customWidth="1" min="38" max="38"/>
-    <col width="15" customWidth="1" min="39" max="39"/>
-    <col width="28" customWidth="1" min="40" max="40"/>
-    <col width="40" customWidth="1" min="41" max="41"/>
+    <col width="12" customWidth="1" min="39" max="39"/>
+    <col width="15" customWidth="1" min="40" max="40"/>
+    <col width="28" customWidth="1" min="41" max="41"/>
     <col width="40" customWidth="1" min="42" max="42"/>
-    <col width="23" customWidth="1" min="43" max="43"/>
+    <col width="40" customWidth="1" min="43" max="43"/>
+    <col width="23" customWidth="1" min="44" max="44"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -703,30 +708,35 @@
       </c>
       <c r="AL2" s="2" t="inlineStr">
         <is>
+          <t>spend_tier</t>
+        </is>
+      </c>
+      <c r="AM2" s="2" t="inlineStr">
+        <is>
           <t>ELIGIBLE</t>
         </is>
       </c>
-      <c r="AM2" s="2" t="inlineStr">
+      <c r="AN2" s="2" t="inlineStr">
         <is>
           <t>OUTREACH_TYPE</t>
         </is>
       </c>
-      <c r="AN2" s="2" t="inlineStr">
+      <c r="AO2" s="2" t="inlineStr">
         <is>
           <t>RECOMMENDED_FOLLOW_UP_DATE</t>
         </is>
       </c>
-      <c r="AO2" s="2" t="inlineStr">
+      <c r="AP2" s="2" t="inlineStr">
         <is>
           <t>SUGGESTED_MESSAGE</t>
         </is>
       </c>
-      <c r="AP2" s="2" t="inlineStr">
+      <c r="AQ2" s="2" t="inlineStr">
         <is>
           <t>MESSAGE_LOGIC</t>
         </is>
       </c>
-      <c r="AQ2" s="2" t="inlineStr">
+      <c r="AR2" s="2" t="inlineStr">
         <is>
           <t>PERSONALISATION_ANGLE</t>
         </is>
@@ -896,26 +906,31 @@
           <t>Missing Contact; Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL3" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM3" s="3" t="inlineStr">
+      <c r="AL3" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM3" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN3" s="3" t="inlineStr">
         <is>
           <t>Inbound</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="n"/>
-      <c r="AO3" s="4" t="inlineStr">
+      <c r="AO3" s="3" t="n"/>
+      <c r="AP3" s="4" t="inlineStr">
         <is>
           <t>Hi there, thanks for getting in touch - I had a look at selling through Depop before writing back. Fleek connects shops like yours with inventory from trusted suppliers, so given your Depop shop, it seemed worth a proper reply rather than a generic one. What's the main gap in sourcing right now - more volume, more variety, or something specific you're struggling to find?</t>
         </is>
       </c>
-      <c r="AP3" s="4" t="inlineStr">
+      <c r="AQ3" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Inbound (Inbound). Personalisation drawn from channel (notes unavailable): selling through Depop. No prior contact on record - treated as first outreach.</t>
         </is>
       </c>
-      <c r="AQ3" s="3" t="inlineStr">
+      <c r="AR3" s="3" t="inlineStr">
         <is>
           <t>selling through Depop</t>
         </is>
@@ -1085,26 +1100,31 @@
           <t>Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL4" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM4" s="3" t="inlineStr">
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
         <is>
           <t>Inbound</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="n"/>
-      <c r="AO4" s="4" t="inlineStr">
+      <c r="AO4" s="3" t="n"/>
+      <c r="AP4" s="4" t="inlineStr">
         <is>
           <t>Hi there, thanks for getting in touch - I had a look at selling through Depop before writing back. Fleek connects shops like yours with inventory from trusted suppliers, so given your Depop shop, it seemed worth a proper reply rather than a generic one. What's the main gap in sourcing right now - more volume, more variety, or something specific you're struggling to find?</t>
         </is>
       </c>
-      <c r="AP4" s="4" t="inlineStr">
+      <c r="AQ4" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Inbound (Inbound). Personalisation drawn from channel (notes unavailable): selling through Depop. No prior contact on record - treated as first outreach.</t>
         </is>
       </c>
-      <c r="AQ4" s="3" t="inlineStr">
+      <c r="AR4" s="3" t="inlineStr">
         <is>
           <t>selling through Depop</t>
         </is>
@@ -1274,26 +1294,31 @@
           <t>Non-UK</t>
         </is>
       </c>
-      <c r="AL5" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM5" s="3" t="inlineStr">
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN5" s="3" t="n"/>
-      <c r="AO5" s="4" t="inlineStr">
+      <c r="AO5" s="3" t="n"/>
+      <c r="AP5" s="4" t="inlineStr">
         <is>
           <t>Hi there, it's been a little while, so wanted to check back in given your curated womenswear built around Levi's and band tees. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP5" s="4" t="inlineStr">
+      <c r="AQ5" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Contacted (Re-Engagement). Personalisation drawn from notes: your curated womenswear built around Levi's and band tees. Last contacted 93 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ5" s="3" t="inlineStr">
+      <c r="AR5" s="3" t="inlineStr">
         <is>
           <t>your curated womenswear built around Levi's and band tees</t>
         </is>
@@ -1463,26 +1488,31 @@
           <t>Missing Contact; Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL6" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM6" s="3" t="inlineStr">
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
         <is>
           <t>Inbound</t>
         </is>
       </c>
-      <c r="AN6" s="3" t="n"/>
-      <c r="AO6" s="4" t="inlineStr">
+      <c r="AO6" s="3" t="n"/>
+      <c r="AP6" s="4" t="inlineStr">
         <is>
           <t>Hi there, thanks for getting in touch - I had a look at running your shop straight through Instagram DMs before writing back. Fleek connects shops like yours with inventory from trusted suppliers, so given the DM-led way you run sales, it seemed worth a proper reply rather than a generic one. What's the main gap in sourcing right now - more volume, more variety, or something specific you're struggling to find?</t>
         </is>
       </c>
-      <c r="AP6" s="4" t="inlineStr">
+      <c r="AQ6" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Inbound (Inbound). Personalisation drawn from notes: running your shop straight through Instagram DMs. No prior contact on record - treated as first outreach.</t>
         </is>
       </c>
-      <c r="AQ6" s="3" t="inlineStr">
+      <c r="AR6" s="3" t="inlineStr">
         <is>
           <t>running your shop straight through Instagram DMs</t>
         </is>
@@ -1652,26 +1682,31 @@
           <t>None</t>
         </is>
       </c>
-      <c r="AL7" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM7" s="3" t="inlineStr">
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN7" s="3" t="n"/>
-      <c r="AO7" s="4" t="inlineStr">
+      <c r="AO7" s="3" t="n"/>
+      <c r="AP7" s="4" t="inlineStr">
         <is>
           <t>Hi there, it's been a little while, so wanted to check back in given your workwear and military surplus range, including Carhartt. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP7" s="4" t="inlineStr">
+      <c r="AQ7" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Contacted (Re-Engagement). Personalisation drawn from notes: your workwear and military surplus range, including Carhartt. Last contacted 50 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ7" s="3" t="inlineStr">
+      <c r="AR7" s="3" t="inlineStr">
         <is>
           <t>your workwear and military surplus range, including Carhartt</t>
         </is>
@@ -1841,26 +1876,31 @@
           <t>Missing Website; Non-UK</t>
         </is>
       </c>
-      <c r="AL8" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM8" s="3" t="inlineStr">
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN8" s="3" t="n"/>
-      <c r="AO8" s="4" t="inlineStr">
+      <c r="AO8" s="3" t="n"/>
+      <c r="AP8" s="4" t="inlineStr">
         <is>
           <t>Hi there, it's been a little while, so wanted to check back in given your 80s/90s denim and sportswear edit. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP8" s="4" t="inlineStr">
+      <c r="AQ8" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Meeting Booked (Re-Engagement). Personalisation drawn from notes: your 80s/90s denim and sportswear edit. Last contacted 42 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ8" s="3" t="inlineStr">
+      <c r="AR8" s="3" t="inlineStr">
         <is>
           <t>your 80s/90s denim and sportswear edit</t>
         </is>
@@ -2030,26 +2070,31 @@
           <t>None</t>
         </is>
       </c>
-      <c r="AL9" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM9" s="3" t="inlineStr">
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
         <is>
           <t>Cold</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="n"/>
-      <c r="AO9" s="4" t="inlineStr">
+      <c r="AO9" s="3" t="n"/>
+      <c r="AP9" s="4" t="inlineStr">
         <is>
           <t>Hi Sam, I came across your shop and noticed your hand-picked edit spanning the 60s through the 90s. I work with Fleek, a wholesale marketplace connecting retailers and resellers with inventory from trusted suppliers and brands. No worries on the missed callback - happy to try again whenever suits. Would it be useful to see what's currently available that fits what you stock?</t>
         </is>
       </c>
-      <c r="AP9" s="4" t="inlineStr">
+      <c r="AQ9" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Contacted (Cold). Personalisation drawn from notes: your hand-picked edit spanning the 60s through the 90s. Notes flagged a specific objection/context, addressed directly rather than ignored. Last contacted 27 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ9" s="3" t="inlineStr">
+      <c r="AR9" s="3" t="inlineStr">
         <is>
           <t>your hand-picked edit spanning the 60s through the 90s</t>
         </is>
@@ -2219,26 +2264,31 @@
           <t>Missing Contact; Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL10" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM10" s="3" t="inlineStr">
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
         <is>
           <t>Churned-Win-Back</t>
         </is>
       </c>
-      <c r="AN10" s="3" t="n"/>
-      <c r="AO10" s="4" t="inlineStr">
+      <c r="AO10" s="3" t="n"/>
+      <c r="AP10" s="4" t="inlineStr">
         <is>
           <t>Hi there, it's been a while since we last worked together, so wanted to reach out honestly rather than pretend nothing's changed. Given the fast sell-through you've been getting, I understand if the timing wasn't right before. Would it be worth a low-pressure conversation about what's changed on our side, in case it's relevant again?</t>
         </is>
       </c>
-      <c r="AP10" s="4" t="inlineStr">
+      <c r="AQ10" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Stopped Buying (Churned-Win-Back). Personalisation drawn from notes: how quickly your stock turns over. Last contacted 87 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ10" s="3" t="inlineStr">
+      <c r="AR10" s="3" t="inlineStr">
         <is>
           <t>how quickly your stock turns over</t>
         </is>
@@ -2408,26 +2458,31 @@
           <t>Missing Contact; Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL11" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM11" s="3" t="inlineStr">
+      <c r="AL11" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM11" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN11" s="3" t="inlineStr">
         <is>
           <t>Churned-Win-Back</t>
         </is>
       </c>
-      <c r="AN11" s="3" t="n"/>
-      <c r="AO11" s="4" t="inlineStr">
+      <c r="AO11" s="3" t="n"/>
+      <c r="AP11" s="4" t="inlineStr">
         <is>
           <t>Hi there, it's been a while since we last worked together, so wanted to reach out honestly rather than pretend nothing's changed. Given the fast sell-through you've been getting, I understand if the timing wasn't right before. Would it be worth a low-pressure conversation about what's changed on our side, in case it's relevant again?</t>
         </is>
       </c>
-      <c r="AP11" s="4" t="inlineStr">
+      <c r="AQ11" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Dormant (Churned-Win-Back). Personalisation drawn from notes: how quickly your stock turns over. Last contacted 76 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ11" s="3" t="inlineStr">
+      <c r="AR11" s="3" t="inlineStr">
         <is>
           <t>how quickly your stock turns over</t>
         </is>
@@ -2597,26 +2652,31 @@
           <t>Missing Contact; Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL12" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM12" s="3" t="inlineStr">
+      <c r="AL12" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN12" s="3" t="n"/>
-      <c r="AO12" s="4" t="inlineStr">
+      <c r="AO12" s="3" t="n"/>
+      <c r="AP12" s="4" t="inlineStr">
         <is>
           <t>Hi there, it's been a little while, so wanted to check back in given running sales through Instagram. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP12" s="4" t="inlineStr">
+      <c r="AQ12" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Contacted (Re-Engagement). Personalisation drawn from channel (notes unavailable): running sales through Instagram. Last contacted 47 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ12" s="3" t="inlineStr">
+      <c r="AR12" s="3" t="inlineStr">
         <is>
           <t>running sales through Instagram</t>
         </is>
@@ -2786,26 +2846,31 @@
           <t>None</t>
         </is>
       </c>
-      <c r="AL13" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM13" s="3" t="inlineStr">
+      <c r="AL13" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM13" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN13" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN13" s="3" t="n"/>
-      <c r="AO13" s="4" t="inlineStr">
+      <c r="AO13" s="3" t="n"/>
+      <c r="AP13" s="4" t="inlineStr">
         <is>
           <t>Hi Ben, it's been a little while, so wanted to check back in given your curated womenswear built around Levi's and band tees. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP13" s="4" t="inlineStr">
+      <c r="AQ13" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Replied (Re-Engagement). Personalisation drawn from notes: your curated womenswear built around Levi's and band tees. Last contacted 79 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ13" s="3" t="inlineStr">
+      <c r="AR13" s="3" t="inlineStr">
         <is>
           <t>your curated womenswear built around Levi's and band tees</t>
         </is>
@@ -2975,27 +3040,32 @@
           <t>Missing Website; Non-UK; Possible Duplicate - Unverified</t>
         </is>
       </c>
-      <c r="AL14" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM14" s="5" t="inlineStr">
+      <c r="AL14" s="5" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="AM14" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN14" s="5" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN14" s="5" t="n"/>
-      <c r="AO14" s="6" t="inlineStr">
+      <c r="AO14" s="5" t="n"/>
+      <c r="AP14" s="6" t="inlineStr">
         <is>
           <t>English: Hi there, it's been a little while, so wanted to check back in given your workwear and military surplus range, including Carhartt. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?
 Translated (French): Bonjour, cela fait un moment, je voulais donc reprendre contact étant donné votre gamme de vêtements de travail et de surplus militaires, y compris Carhartt. Aucune pression si le moment n'est plus idéal, mais si l'approvisionnement reste d'actualité, je serais ravi d'en reparler. Cela vaudrait-il la peine d'en discuter rapidement ?</t>
         </is>
       </c>
-      <c r="AP14" s="6" t="inlineStr">
+      <c r="AQ14" s="6" t="inlineStr">
         <is>
           <t>Stage identified as Contacted (Re-Engagement). Personalisation drawn from notes: your workwear and military surplus range, including Carhartt. Last contacted 45 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ14" s="5" t="inlineStr">
+      <c r="AR14" s="5" t="inlineStr">
         <is>
           <t>your workwear and military surplus range, including Carhartt</t>
         </is>
@@ -3165,26 +3235,31 @@
           <t>Missing Contact; Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL15" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM15" s="3" t="inlineStr">
+      <c r="AL15" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM15" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN15" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN15" s="3" t="n"/>
-      <c r="AO15" s="4" t="inlineStr">
+      <c r="AO15" s="3" t="n"/>
+      <c r="AP15" s="4" t="inlineStr">
         <is>
           <t>Hi there, it's been a little while, so wanted to check back in given your live-sale presence on Whatnot. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP15" s="4" t="inlineStr">
+      <c r="AQ15" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Replied (Re-Engagement). Personalisation drawn from channel (notes unavailable): your live-sale presence on Whatnot. Last contacted 64 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ15" s="3" t="inlineStr">
+      <c r="AR15" s="3" t="inlineStr">
         <is>
           <t>your live-sale presence on Whatnot</t>
         </is>
@@ -3354,26 +3429,31 @@
           <t>Missing Contact; Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL16" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM16" s="3" t="inlineStr">
+      <c r="AL16" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM16" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN16" s="3" t="inlineStr">
         <is>
           <t>Cold</t>
         </is>
       </c>
-      <c r="AN16" s="3" t="n"/>
-      <c r="AO16" s="4" t="inlineStr">
+      <c r="AO16" s="3" t="n"/>
+      <c r="AP16" s="4" t="inlineStr">
         <is>
           <t>Hi there, I came across your shop and noticed how quickly your stock turns over. I work with Fleek, a wholesale marketplace connecting retailers and resellers with inventory from trusted suppliers and brands. Would it be useful to see what's currently available that fits what you stock?</t>
         </is>
       </c>
-      <c r="AP16" s="4" t="inlineStr">
+      <c r="AQ16" s="4" t="inlineStr">
         <is>
           <t>Stage identified as New Lead (Cold). Personalisation drawn from notes: how quickly your stock turns over. No prior contact on record - treated as first outreach.</t>
         </is>
       </c>
-      <c r="AQ16" s="3" t="inlineStr">
+      <c r="AR16" s="3" t="inlineStr">
         <is>
           <t>how quickly your stock turns over</t>
         </is>
@@ -3543,26 +3623,31 @@
           <t>Missing Contact; Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL17" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM17" s="3" t="inlineStr">
+      <c r="AL17" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM17" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN17" s="3" t="n"/>
-      <c r="AO17" s="4" t="inlineStr">
+      <c r="AO17" s="3" t="n"/>
+      <c r="AP17" s="4" t="inlineStr">
         <is>
           <t>Hi there, it's been a little while, so wanted to check back in given selling across both Depop and Vinted. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP17" s="4" t="inlineStr">
+      <c r="AQ17" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Contacted (Re-Engagement). Personalisation drawn from notes: selling across both Depop and Vinted. Last contacted 56 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ17" s="3" t="inlineStr">
+      <c r="AR17" s="3" t="inlineStr">
         <is>
           <t>selling across both Depop and Vinted</t>
         </is>
@@ -3732,26 +3817,31 @@
           <t>None</t>
         </is>
       </c>
-      <c r="AL18" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM18" s="3" t="inlineStr">
+      <c r="AL18" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM18" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
         <is>
           <t>Customer Check-In</t>
         </is>
       </c>
-      <c r="AN18" s="3" t="n"/>
-      <c r="AO18" s="4" t="inlineStr">
+      <c r="AO18" s="3" t="n"/>
+      <c r="AP18" s="4" t="inlineStr">
         <is>
           <t>Hi Ben, wanted to check in properly rather than send a generic update, given the 80s/90s denim and sportswear range you've built. Keen to hear how things have been going and whether there's anything new worth exploring together. Any gaps in what you're sourcing at the moment, or new ranges you're thinking about?</t>
         </is>
       </c>
-      <c r="AP18" s="4" t="inlineStr">
+      <c r="AQ18" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Closed Won (Customer Check-In). Personalisation drawn from notes: your 80s/90s denim and sportswear edit. Last contacted 26 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ18" s="3" t="inlineStr">
+      <c r="AR18" s="3" t="inlineStr">
         <is>
           <t>your 80s/90s denim and sportswear edit</t>
         </is>
@@ -3921,26 +4011,31 @@
           <t>Missing Website</t>
         </is>
       </c>
-      <c r="AL19" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM19" s="3" t="inlineStr">
+      <c r="AL19" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM19" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN19" s="3" t="inlineStr">
         <is>
           <t>Churned-Win-Back</t>
         </is>
       </c>
-      <c r="AN19" s="3" t="n"/>
-      <c r="AO19" s="4" t="inlineStr">
+      <c r="AO19" s="3" t="n"/>
+      <c r="AP19" s="4" t="inlineStr">
         <is>
           <t>Hi Rosa, it's been a while since we last worked together, so wanted to reach out honestly rather than pretend nothing's changed. Given the football shirt and sportswear range you specialise in, I understand if the timing wasn't right before. Makes sense to see it in action first - I can walk you through the app directly rather than describe it. Would it be worth a low-pressure conversation about what's changed on our side, in case it's relevant again?</t>
         </is>
       </c>
-      <c r="AP19" s="4" t="inlineStr">
+      <c r="AQ19" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Lapsed (Churned-Win-Back). Personalisation drawn from notes: your retro football shirt and vintage sportswear range. Notes flagged a specific objection/context, addressed directly rather than ignored. Last contacted 107 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ19" s="3" t="inlineStr">
+      <c r="AR19" s="3" t="inlineStr">
         <is>
           <t>your retro football shirt and vintage sportswear range</t>
         </is>
@@ -4110,26 +4205,31 @@
           <t>Missing Contact; Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL20" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM20" s="3" t="inlineStr">
+      <c r="AL20" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM20" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN20" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN20" s="3" t="n"/>
-      <c r="AO20" s="4" t="inlineStr">
+      <c r="AO20" s="3" t="n"/>
+      <c r="AP20" s="4" t="inlineStr">
         <is>
           <t>Hi there, it's been a little while, so wanted to check back in given selling across both Depop and Vinted. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP20" s="4" t="inlineStr">
+      <c r="AQ20" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Contacted (Re-Engagement). Personalisation drawn from notes: selling across both Depop and Vinted. Last contacted 97 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ20" s="3" t="inlineStr">
+      <c r="AR20" s="3" t="inlineStr">
         <is>
           <t>selling across both Depop and Vinted</t>
         </is>
@@ -4299,22 +4399,27 @@
           <t>Missing Website</t>
         </is>
       </c>
-      <c r="AL21" s="3" t="b">
+      <c r="AL21" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM21" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="AM21" s="3" t="inlineStr">
+      <c r="AN21" s="3" t="inlineStr">
         <is>
           <t>No Action</t>
         </is>
       </c>
-      <c r="AN21" s="3" t="n"/>
-      <c r="AO21" s="4" t="inlineStr"/>
-      <c r="AP21" s="4" t="inlineStr">
+      <c r="AO21" s="3" t="n"/>
+      <c r="AP21" s="4" t="inlineStr"/>
+      <c r="AQ21" s="4" t="inlineStr">
         <is>
           <t>Stage 'In Conversation' is on the do-not-message list - no message drafted, no assumptions made about prior conversation content.</t>
         </is>
       </c>
-      <c r="AQ21" s="3" t="inlineStr"/>
+      <c r="AR21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -4480,26 +4585,31 @@
           <t>Possible Duplicate - Unverified</t>
         </is>
       </c>
-      <c r="AL22" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM22" s="5" t="inlineStr">
+      <c r="AL22" s="5" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM22" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN22" s="5" t="inlineStr">
         <is>
           <t>Inbound</t>
         </is>
       </c>
-      <c r="AN22" s="5" t="n"/>
-      <c r="AO22" s="6" t="inlineStr">
+      <c r="AO22" s="5" t="n"/>
+      <c r="AP22" s="6" t="inlineStr">
         <is>
           <t>Hi there, thanks for getting in touch - I had a look at your Y2K, grunge and reworked one-off pieces before writing back. Fleek connects shops like yours with inventory from trusted suppliers, so given the Y2K and grunge one-offs you carry, it seemed worth a proper reply rather than a generic one. What's the main gap in sourcing right now - more volume, more variety, or something specific you're struggling to find?</t>
         </is>
       </c>
-      <c r="AP22" s="6" t="inlineStr">
+      <c r="AQ22" s="6" t="inlineStr">
         <is>
           <t>Stage identified as Inbound (Inbound). Personalisation drawn from notes: your Y2K, grunge and reworked one-off pieces. No prior contact on record - treated as first outreach.</t>
         </is>
       </c>
-      <c r="AQ22" s="5" t="inlineStr">
+      <c r="AR22" s="5" t="inlineStr">
         <is>
           <t>your Y2K, grunge and reworked one-off pieces</t>
         </is>
@@ -4669,22 +4779,27 @@
           <t>Missing Website</t>
         </is>
       </c>
-      <c r="AL23" s="3" t="b">
+      <c r="AL23" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM23" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="AM23" s="3" t="inlineStr">
+      <c r="AN23" s="3" t="inlineStr">
         <is>
           <t>No Action</t>
         </is>
       </c>
-      <c r="AN23" s="3" t="n"/>
-      <c r="AO23" s="4" t="inlineStr"/>
-      <c r="AP23" s="4" t="inlineStr">
+      <c r="AO23" s="3" t="n"/>
+      <c r="AP23" s="4" t="inlineStr"/>
+      <c r="AQ23" s="4" t="inlineStr">
         <is>
           <t>Stage 'In Conversation' is on the do-not-message list - no message drafted, no assumptions made about prior conversation content.</t>
         </is>
       </c>
-      <c r="AQ23" s="3" t="inlineStr"/>
+      <c r="AR23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -4850,26 +4965,31 @@
           <t>Missing Contact; Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL24" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM24" s="3" t="inlineStr">
+      <c r="AL24" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM24" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN24" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN24" s="3" t="n"/>
-      <c r="AO24" s="4" t="inlineStr">
+      <c r="AO24" s="3" t="n"/>
+      <c r="AP24" s="4" t="inlineStr">
         <is>
           <t>Hi there, it's been a little while, so wanted to check back in given your live-sale format on Whatnot. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP24" s="4" t="inlineStr">
+      <c r="AQ24" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Contacted (Re-Engagement). Personalisation drawn from notes: your live-sale format on Whatnot. Last contacted 67 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ24" s="3" t="inlineStr">
+      <c r="AR24" s="3" t="inlineStr">
         <is>
           <t>your live-sale format on Whatnot</t>
         </is>
@@ -5039,26 +5159,31 @@
           <t>Missing Instagram</t>
         </is>
       </c>
-      <c r="AL25" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM25" s="3" t="inlineStr">
+      <c r="AL25" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM25" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN25" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN25" s="3" t="n"/>
-      <c r="AO25" s="4" t="inlineStr">
+      <c r="AO25" s="3" t="n"/>
+      <c r="AP25" s="4" t="inlineStr">
         <is>
           <t>Hi Jack, it's been a little while, so wanted to check back in given your workwear and military surplus range, including Carhartt. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP25" s="4" t="inlineStr">
+      <c r="AQ25" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Visit Booked (Re-Engagement). Personalisation drawn from notes: your workwear and military surplus range, including Carhartt. Last contacted 49 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ25" s="3" t="inlineStr">
+      <c r="AR25" s="3" t="inlineStr">
         <is>
           <t>your workwear and military surplus range, including Carhartt</t>
         </is>
@@ -5228,26 +5353,31 @@
           <t>None</t>
         </is>
       </c>
-      <c r="AL26" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM26" s="3" t="inlineStr">
+      <c r="AL26" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM26" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN26" s="3" t="inlineStr">
         <is>
           <t>Cold</t>
         </is>
       </c>
-      <c r="AN26" s="3" t="n"/>
-      <c r="AO26" s="4" t="inlineStr">
+      <c r="AO26" s="3" t="n"/>
+      <c r="AP26" s="4" t="inlineStr">
         <is>
           <t>Hi James, I came across your shop and noticed your hand-picked edit spanning the 60s through the 90s. I work with Fleek, a wholesale marketplace connecting retailers and resellers with inventory from trusted suppliers and brands. Would it be useful to see what's currently available that fits what you stock?</t>
         </is>
       </c>
-      <c r="AP26" s="4" t="inlineStr">
+      <c r="AQ26" s="4" t="inlineStr">
         <is>
           <t>Stage identified as New Lead (Cold). Personalisation drawn from notes: your hand-picked edit spanning the 60s through the 90s. No prior contact on record - treated as first outreach.</t>
         </is>
       </c>
-      <c r="AQ26" s="3" t="inlineStr">
+      <c r="AR26" s="3" t="inlineStr">
         <is>
           <t>your hand-picked edit spanning the 60s through the 90s</t>
         </is>
@@ -5417,27 +5547,32 @@
           <t>Missing Contact; Missing Instagram; Non-UK</t>
         </is>
       </c>
-      <c r="AL27" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM27" s="3" t="inlineStr">
+      <c r="AL27" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM27" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN27" s="3" t="inlineStr">
         <is>
           <t>Cold</t>
         </is>
       </c>
-      <c r="AN27" s="3" t="n"/>
-      <c r="AO27" s="4" t="inlineStr">
+      <c r="AO27" s="3" t="n"/>
+      <c r="AP27" s="4" t="inlineStr">
         <is>
           <t>English: Hi Theo, I came across your shop and noticed your reworked and archive designer pieces. I work with Fleek, a wholesale marketplace connecting retailers and resellers with inventory from trusted suppliers and brands. Would it be useful to see what's currently available that fits what you stock?
 Translated (Dutch): Hallo Theo, ik kwam uw winkel tegen en merkte uw bewerkte stukken en designer-archiefstukken op. Ik werk met Fleek, een groothandelsmarktplaats die retailers en resellers verbindt met voorraad van betrouwbare leveranciers en merken. Zou het interessant zijn om te zien wat er nu beschikbaar is en aansluit bij wat u verkoopt?</t>
         </is>
       </c>
-      <c r="AP27" s="4" t="inlineStr">
+      <c r="AQ27" s="4" t="inlineStr">
         <is>
           <t>Stage identified as New Lead (Cold). Personalisation drawn from notes: your reworked and archive designer pieces. No prior contact on record - treated as first outreach.</t>
         </is>
       </c>
-      <c r="AQ27" s="3" t="inlineStr">
+      <c r="AR27" s="3" t="inlineStr">
         <is>
           <t>your reworked and archive designer pieces</t>
         </is>
@@ -5607,26 +5742,31 @@
           <t>Missing Contact; Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL28" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM28" s="3" t="inlineStr">
+      <c r="AL28" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM28" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN28" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN28" s="3" t="n"/>
-      <c r="AO28" s="4" t="inlineStr">
+      <c r="AO28" s="3" t="n"/>
+      <c r="AP28" s="4" t="inlineStr">
         <is>
           <t>Hi there, it's been a little while, so wanted to check back in given your live-sale presence on Whatnot. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP28" s="4" t="inlineStr">
+      <c r="AQ28" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Replied (Re-Engagement). Personalisation drawn from channel (notes unavailable): your live-sale presence on Whatnot. Last contacted 43 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ28" s="3" t="inlineStr">
+      <c r="AR28" s="3" t="inlineStr">
         <is>
           <t>your live-sale presence on Whatnot</t>
         </is>
@@ -5796,26 +5936,31 @@
           <t>Missing Instagram</t>
         </is>
       </c>
-      <c r="AL29" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM29" s="3" t="inlineStr">
+      <c r="AL29" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM29" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN29" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN29" s="3" t="n"/>
-      <c r="AO29" s="4" t="inlineStr">
+      <c r="AO29" s="3" t="n"/>
+      <c r="AP29" s="4" t="inlineStr">
         <is>
           <t>Hi Ben, it's been a little while, so wanted to check back in given running sales through Instagram. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP29" s="4" t="inlineStr">
+      <c r="AQ29" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Quote Sent (Re-Engagement). Personalisation drawn from channel (notes unavailable): running sales through Instagram. Last contacted 23 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ29" s="3" t="inlineStr">
+      <c r="AR29" s="3" t="inlineStr">
         <is>
           <t>running sales through Instagram</t>
         </is>
@@ -5985,26 +6130,31 @@
           <t>None</t>
         </is>
       </c>
-      <c r="AL30" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM30" s="3" t="inlineStr">
+      <c r="AL30" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM30" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN30" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN30" s="3" t="n"/>
-      <c r="AO30" s="4" t="inlineStr">
+      <c r="AO30" s="3" t="n"/>
+      <c r="AP30" s="4" t="inlineStr">
         <is>
           <t>Hi there, it's been a little while, so wanted to check back in given your hand-picked edit spanning the 60s through the 90s. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP30" s="4" t="inlineStr">
+      <c r="AQ30" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Negotiating (Re-Engagement). Personalisation drawn from notes: your hand-picked edit spanning the 60s through the 90s. Last contacted 66 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ30" s="3" t="inlineStr">
+      <c r="AR30" s="3" t="inlineStr">
         <is>
           <t>your hand-picked edit spanning the 60s through the 90s</t>
         </is>
@@ -6174,22 +6324,27 @@
           <t>Missing Contact; Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL31" s="3" t="b">
+      <c r="AL31" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM31" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="AM31" s="3" t="inlineStr">
+      <c r="AN31" s="3" t="inlineStr">
         <is>
           <t>No Action</t>
         </is>
       </c>
-      <c r="AN31" s="3" t="n"/>
-      <c r="AO31" s="4" t="inlineStr"/>
-      <c r="AP31" s="4" t="inlineStr">
+      <c r="AO31" s="3" t="n"/>
+      <c r="AP31" s="4" t="inlineStr"/>
+      <c r="AQ31" s="4" t="inlineStr">
         <is>
           <t>Stage 'Closed Lost' is on the do-not-message list - no message drafted, no assumptions made about prior conversation content.</t>
         </is>
       </c>
-      <c r="AQ31" s="3" t="inlineStr"/>
+      <c r="AR31" s="3" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -6355,26 +6510,31 @@
           <t>Missing Contact; Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL32" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM32" s="3" t="inlineStr">
+      <c r="AL32" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM32" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN32" s="3" t="inlineStr">
         <is>
           <t>Cold</t>
         </is>
       </c>
-      <c r="AN32" s="3" t="n"/>
-      <c r="AO32" s="4" t="inlineStr">
+      <c r="AO32" s="3" t="n"/>
+      <c r="AP32" s="4" t="inlineStr">
         <is>
           <t>Hi there, I came across your shop and noticed selling across both Depop and Vinted. I work with Fleek, a wholesale marketplace connecting retailers and resellers with inventory from trusted suppliers and brands. Would it be useful to see what's currently available that fits what you stock?</t>
         </is>
       </c>
-      <c r="AP32" s="4" t="inlineStr">
+      <c r="AQ32" s="4" t="inlineStr">
         <is>
           <t>Stage identified as New Lead (Cold). Personalisation drawn from notes: selling across both Depop and Vinted. No prior contact on record - treated as first outreach.</t>
         </is>
       </c>
-      <c r="AQ32" s="3" t="inlineStr">
+      <c r="AR32" s="3" t="inlineStr">
         <is>
           <t>selling across both Depop and Vinted</t>
         </is>
@@ -6544,26 +6704,31 @@
           <t>Missing Contact; Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL33" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM33" s="3" t="inlineStr">
+      <c r="AL33" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM33" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN33" s="3" t="inlineStr">
         <is>
           <t>Cold</t>
         </is>
       </c>
-      <c r="AN33" s="3" t="n"/>
-      <c r="AO33" s="4" t="inlineStr">
+      <c r="AO33" s="3" t="n"/>
+      <c r="AP33" s="4" t="inlineStr">
         <is>
           <t>Hi there, I came across your shop and noticed selling through Vinted. I work with Fleek, a wholesale marketplace connecting retailers and resellers with inventory from trusted suppliers and brands. Would it be useful to see what's currently available that fits what you stock?</t>
         </is>
       </c>
-      <c r="AP33" s="4" t="inlineStr">
+      <c r="AQ33" s="4" t="inlineStr">
         <is>
           <t>Stage identified as New Lead (Cold). Personalisation drawn from channel (notes unavailable): selling through Vinted. No prior contact on record - treated as first outreach.</t>
         </is>
       </c>
-      <c r="AQ33" s="3" t="inlineStr">
+      <c r="AR33" s="3" t="inlineStr">
         <is>
           <t>selling through Vinted</t>
         </is>
@@ -6733,26 +6898,31 @@
           <t>Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL34" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM34" s="3" t="inlineStr">
+      <c r="AL34" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM34" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN34" s="3" t="inlineStr">
         <is>
           <t>Inbound</t>
         </is>
       </c>
-      <c r="AN34" s="3" t="n"/>
-      <c r="AO34" s="4" t="inlineStr">
+      <c r="AO34" s="3" t="n"/>
+      <c r="AP34" s="4" t="inlineStr">
         <is>
           <t>Hi there, thanks for getting in touch - I had a look at selling through Vinted before writing back. Fleek connects shops like yours with inventory from trusted suppliers, so given your Vinted shop, it seemed worth a proper reply rather than a generic one. What's the main gap in sourcing right now - more volume, more variety, or something specific you're struggling to find?</t>
         </is>
       </c>
-      <c r="AP34" s="4" t="inlineStr">
+      <c r="AQ34" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Inbound (Inbound). Personalisation drawn from channel (notes unavailable): selling through Vinted. No prior contact on record - treated as first outreach.</t>
         </is>
       </c>
-      <c r="AQ34" s="3" t="inlineStr">
+      <c r="AR34" s="3" t="inlineStr">
         <is>
           <t>selling through Vinted</t>
         </is>
@@ -6922,26 +7092,31 @@
           <t>Missing Contact; Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL35" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM35" s="3" t="inlineStr">
+      <c r="AL35" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM35" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN35" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN35" s="3" t="n"/>
-      <c r="AO35" s="4" t="inlineStr">
+      <c r="AO35" s="3" t="n"/>
+      <c r="AP35" s="4" t="inlineStr">
         <is>
           <t>Hi there, it's been a little while, so wanted to check back in given running your shop straight through Instagram DMs. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP35" s="4" t="inlineStr">
+      <c r="AQ35" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Trial Pending (Re-Engagement). Personalisation drawn from notes: running your shop straight through Instagram DMs. Last contacted 74 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ35" s="3" t="inlineStr">
+      <c r="AR35" s="3" t="inlineStr">
         <is>
           <t>running your shop straight through Instagram DMs</t>
         </is>
@@ -7111,22 +7286,27 @@
           <t>Missing Contact; Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL36" s="3" t="b">
+      <c r="AL36" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM36" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="AM36" s="3" t="inlineStr">
+      <c r="AN36" s="3" t="inlineStr">
         <is>
           <t>No Action</t>
         </is>
       </c>
-      <c r="AN36" s="3" t="n"/>
-      <c r="AO36" s="4" t="inlineStr"/>
-      <c r="AP36" s="4" t="inlineStr">
+      <c r="AO36" s="3" t="n"/>
+      <c r="AP36" s="4" t="inlineStr"/>
+      <c r="AQ36" s="4" t="inlineStr">
         <is>
           <t>Stage 'In Conversation' is on the do-not-message list - no message drafted, no assumptions made about prior conversation content.</t>
         </is>
       </c>
-      <c r="AQ36" s="3" t="inlineStr"/>
+      <c r="AR36" s="3" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -7292,22 +7472,27 @@
           <t>None</t>
         </is>
       </c>
-      <c r="AL37" s="3" t="b">
+      <c r="AL37" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM37" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="AM37" s="3" t="inlineStr">
+      <c r="AN37" s="3" t="inlineStr">
         <is>
           <t>No Action</t>
         </is>
       </c>
-      <c r="AN37" s="3" t="n"/>
-      <c r="AO37" s="4" t="inlineStr"/>
-      <c r="AP37" s="4" t="inlineStr">
+      <c r="AO37" s="3" t="n"/>
+      <c r="AP37" s="4" t="inlineStr"/>
+      <c r="AQ37" s="4" t="inlineStr">
         <is>
           <t>Stage 'In Conversation' is on the do-not-message list - no message drafted, no assumptions made about prior conversation content.</t>
         </is>
       </c>
-      <c r="AQ37" s="3" t="inlineStr"/>
+      <c r="AR37" s="3" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -7473,27 +7658,32 @@
           <t>Missing Contact; Non-UK</t>
         </is>
       </c>
-      <c r="AL38" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM38" s="3" t="inlineStr">
+      <c r="AL38" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM38" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN38" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN38" s="3" t="n"/>
-      <c r="AO38" s="4" t="inlineStr">
+      <c r="AO38" s="3" t="n"/>
+      <c r="AP38" s="4" t="inlineStr">
         <is>
           <t>English: Hi there, it's been a little while, so wanted to check back in given your reworked and archive designer pieces. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?
 Translated (French): Bonjour, cela fait un moment, je voulais donc reprendre contact étant donné vos pièces retravaillées et vos pièces d'archives de créateurs. Aucune pression si le moment n'est plus idéal, mais si l'approvisionnement reste d'actualité, je serais ravi d'en reparler. Cela vaudrait-il la peine d'en discuter rapidement ?</t>
         </is>
       </c>
-      <c r="AP38" s="4" t="inlineStr">
+      <c r="AQ38" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Negotiating (Re-Engagement). Personalisation drawn from notes: your reworked and archive designer pieces. Last contacted 26 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ38" s="3" t="inlineStr">
+      <c r="AR38" s="3" t="inlineStr">
         <is>
           <t>your reworked and archive designer pieces</t>
         </is>
@@ -7663,26 +7853,31 @@
           <t>Missing Website</t>
         </is>
       </c>
-      <c r="AL39" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM39" s="3" t="inlineStr">
+      <c r="AL39" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM39" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN39" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN39" s="3" t="n"/>
-      <c r="AO39" s="4" t="inlineStr">
+      <c r="AO39" s="3" t="n"/>
+      <c r="AP39" s="4" t="inlineStr">
         <is>
           <t>Hi there, it's been a little while, so wanted to check back in given your 80s/90s denim and sportswear edit. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. The sizing-mix issue from 2023 was a fair complaint, and the way we curate mixes has changed since - genuinely curious whether it's worth a second look. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP39" s="4" t="inlineStr">
+      <c r="AQ39" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Replied (Re-Engagement). Personalisation drawn from notes: your 80s/90s denim and sportswear edit. Notes flagged a specific objection/context, addressed directly rather than ignored. Last contacted 73 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ39" s="3" t="inlineStr">
+      <c r="AR39" s="3" t="inlineStr">
         <is>
           <t>your 80s/90s denim and sportswear edit</t>
         </is>
@@ -7852,26 +8047,31 @@
           <t>Missing Contact; Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL40" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM40" s="3" t="inlineStr">
+      <c r="AL40" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM40" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN40" s="3" t="inlineStr">
         <is>
           <t>Cold</t>
         </is>
       </c>
-      <c r="AN40" s="3" t="n"/>
-      <c r="AO40" s="4" t="inlineStr">
+      <c r="AO40" s="3" t="n"/>
+      <c r="AP40" s="4" t="inlineStr">
         <is>
           <t>Hi there, I came across your shop and noticed your live-sale format on Whatnot. I work with Fleek, a wholesale marketplace connecting retailers and resellers with inventory from trusted suppliers and brands. Would it be useful to see what's currently available that fits what you stock?</t>
         </is>
       </c>
-      <c r="AP40" s="4" t="inlineStr">
+      <c r="AQ40" s="4" t="inlineStr">
         <is>
           <t>Stage identified as New Lead (Cold). Personalisation drawn from notes: your live-sale format on Whatnot. No prior contact on record - treated as first outreach.</t>
         </is>
       </c>
-      <c r="AQ40" s="3" t="inlineStr">
+      <c r="AR40" s="3" t="inlineStr">
         <is>
           <t>your live-sale format on Whatnot</t>
         </is>
@@ -8041,26 +8241,31 @@
           <t>Missing Contact; Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL41" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM41" s="3" t="inlineStr">
+      <c r="AL41" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM41" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN41" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN41" s="3" t="n"/>
-      <c r="AO41" s="4" t="inlineStr">
+      <c r="AO41" s="3" t="n"/>
+      <c r="AP41" s="4" t="inlineStr">
         <is>
           <t>Hi there, it's been a little while, so wanted to check back in given selling through Vinted. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP41" s="4" t="inlineStr">
+      <c r="AQ41" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Contacted (Re-Engagement). Personalisation drawn from channel (notes unavailable): selling through Vinted. Last contacted 79 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ41" s="3" t="inlineStr">
+      <c r="AR41" s="3" t="inlineStr">
         <is>
           <t>selling through Vinted</t>
         </is>
@@ -8230,26 +8435,31 @@
           <t>Non-UK</t>
         </is>
       </c>
-      <c r="AL42" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM42" s="3" t="inlineStr">
+      <c r="AL42" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM42" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN42" s="3" t="inlineStr">
         <is>
           <t>Customer Check-In</t>
         </is>
       </c>
-      <c r="AN42" s="3" t="n"/>
-      <c r="AO42" s="4" t="inlineStr">
+      <c r="AO42" s="3" t="n"/>
+      <c r="AP42" s="4" t="inlineStr">
         <is>
           <t>Hi Grace, wanted to check in properly rather than send a generic update, given the reworked, archive-designer side of what you stock. Keen to hear how things have been going and whether there's anything new worth exploring together. Any gaps in what you're sourcing at the moment, or new ranges you're thinking about?</t>
         </is>
       </c>
-      <c r="AP42" s="4" t="inlineStr">
+      <c r="AQ42" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Closed Won (Customer Check-In). Personalisation drawn from notes: your reworked and archive designer pieces. Last contacted 65 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ42" s="3" t="inlineStr">
+      <c r="AR42" s="3" t="inlineStr">
         <is>
           <t>your reworked and archive designer pieces</t>
         </is>
@@ -8419,26 +8629,31 @@
           <t>Non-UK</t>
         </is>
       </c>
-      <c r="AL43" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM43" s="3" t="inlineStr">
+      <c r="AL43" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM43" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN43" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN43" s="3" t="n"/>
-      <c r="AO43" s="4" t="inlineStr">
+      <c r="AO43" s="3" t="n"/>
+      <c r="AP43" s="4" t="inlineStr">
         <is>
           <t>Hi Yusuf, it's been a little while, so wanted to check back in given your hand-picked edit spanning the 60s through the 90s. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP43" s="4" t="inlineStr">
+      <c r="AQ43" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Replied (Re-Engagement). Personalisation drawn from notes: your hand-picked edit spanning the 60s through the 90s. Last contacted 121 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ43" s="3" t="inlineStr">
+      <c r="AR43" s="3" t="inlineStr">
         <is>
           <t>your hand-picked edit spanning the 60s through the 90s</t>
         </is>
@@ -8608,26 +8823,31 @@
           <t>Missing Website</t>
         </is>
       </c>
-      <c r="AL44" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM44" s="3" t="inlineStr">
+      <c r="AL44" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM44" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN44" s="3" t="inlineStr">
         <is>
           <t>Cold</t>
         </is>
       </c>
-      <c r="AN44" s="3" t="n"/>
-      <c r="AO44" s="4" t="inlineStr">
+      <c r="AO44" s="3" t="n"/>
+      <c r="AP44" s="4" t="inlineStr">
         <is>
           <t>Hi Noor, I came across your shop and noticed your workwear and military surplus range, including Carhartt. I work with Fleek, a wholesale marketplace connecting retailers and resellers with inventory from trusted suppliers and brands. Would it be useful to see what's currently available that fits what you stock?</t>
         </is>
       </c>
-      <c r="AP44" s="4" t="inlineStr">
+      <c r="AQ44" s="4" t="inlineStr">
         <is>
           <t>Stage identified as New Lead (Cold). Personalisation drawn from notes: your workwear and military surplus range, including Carhartt. No prior contact on record - treated as first outreach.</t>
         </is>
       </c>
-      <c r="AQ44" s="3" t="inlineStr">
+      <c r="AR44" s="3" t="inlineStr">
         <is>
           <t>your workwear and military surplus range, including Carhartt</t>
         </is>
@@ -8797,26 +9017,31 @@
           <t>Missing Contact; Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL45" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM45" s="3" t="inlineStr">
+      <c r="AL45" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM45" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN45" s="3" t="inlineStr">
         <is>
           <t>Customer Check-In</t>
         </is>
       </c>
-      <c r="AN45" s="3" t="n"/>
-      <c r="AO45" s="4" t="inlineStr">
+      <c r="AO45" s="3" t="n"/>
+      <c r="AP45" s="4" t="inlineStr">
         <is>
           <t>Hi there, wanted to check in properly rather than send a generic update, given the live-sale format you run on Whatnot. Keen to hear how things have been going and whether there's anything new worth exploring together. Any gaps in what you're sourcing at the moment, or new ranges you're thinking about?</t>
         </is>
       </c>
-      <c r="AP45" s="4" t="inlineStr">
+      <c r="AQ45" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Closed Won (Customer Check-In). Personalisation drawn from notes: your live-sale format on Whatnot. Last contacted 55 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ45" s="3" t="inlineStr">
+      <c r="AR45" s="3" t="inlineStr">
         <is>
           <t>your live-sale format on Whatnot</t>
         </is>
@@ -8986,26 +9211,31 @@
           <t>Missing Instagram</t>
         </is>
       </c>
-      <c r="AL46" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM46" s="3" t="inlineStr">
+      <c r="AL46" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM46" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN46" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN46" s="3" t="n"/>
-      <c r="AO46" s="4" t="inlineStr">
+      <c r="AO46" s="3" t="n"/>
+      <c r="AP46" s="4" t="inlineStr">
         <is>
           <t>Hi Ellie, it's been a little while, so wanted to check back in given your 80s/90s denim and sportswear edit. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP46" s="4" t="inlineStr">
+      <c r="AQ46" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Quote Sent (Re-Engagement). Personalisation drawn from notes: your 80s/90s denim and sportswear edit. Last contacted 69 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ46" s="3" t="inlineStr">
+      <c r="AR46" s="3" t="inlineStr">
         <is>
           <t>your 80s/90s denim and sportswear edit</t>
         </is>
@@ -9175,26 +9405,31 @@
           <t>Missing Contact; Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL47" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM47" s="3" t="inlineStr">
+      <c r="AL47" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM47" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN47" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN47" s="3" t="n"/>
-      <c r="AO47" s="4" t="inlineStr">
+      <c r="AO47" s="3" t="n"/>
+      <c r="AP47" s="4" t="inlineStr">
         <is>
           <t>Hi there, it's been a little while, so wanted to check back in given how quickly your stock turns over. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP47" s="4" t="inlineStr">
+      <c r="AQ47" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Replied (Re-Engagement). Personalisation drawn from notes: how quickly your stock turns over. Last contacted 51 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ47" s="3" t="inlineStr">
+      <c r="AR47" s="3" t="inlineStr">
         <is>
           <t>how quickly your stock turns over</t>
         </is>
@@ -9364,26 +9599,31 @@
           <t>None</t>
         </is>
       </c>
-      <c r="AL48" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM48" s="3" t="inlineStr">
+      <c r="AL48" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM48" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN48" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN48" s="3" t="n"/>
-      <c r="AO48" s="4" t="inlineStr">
+      <c r="AO48" s="3" t="n"/>
+      <c r="AP48" s="4" t="inlineStr">
         <is>
           <t>Hi there, it's been a little while, so wanted to check back in given your workwear and military surplus range, including Carhartt. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Happy to work around your weekend trade - midweek suits us fine. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP48" s="4" t="inlineStr">
+      <c r="AQ48" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Replied (Re-Engagement). Personalisation drawn from notes: your workwear and military surplus range, including Carhartt. Notes flagged a specific objection/context, addressed directly rather than ignored. Last contacted 17 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ48" s="3" t="inlineStr">
+      <c r="AR48" s="3" t="inlineStr">
         <is>
           <t>your workwear and military surplus range, including Carhartt</t>
         </is>
@@ -9553,22 +9793,27 @@
           <t>None</t>
         </is>
       </c>
-      <c r="AL49" s="3" t="b">
+      <c r="AL49" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM49" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="AM49" s="3" t="inlineStr">
+      <c r="AN49" s="3" t="inlineStr">
         <is>
           <t>No Action</t>
         </is>
       </c>
-      <c r="AN49" s="3" t="n"/>
-      <c r="AO49" s="4" t="inlineStr"/>
-      <c r="AP49" s="4" t="inlineStr">
+      <c r="AO49" s="3" t="n"/>
+      <c r="AP49" s="4" t="inlineStr"/>
+      <c r="AQ49" s="4" t="inlineStr">
         <is>
           <t>Stage 'Closed Lost' is on the do-not-message list - no message drafted, no assumptions made about prior conversation content.</t>
         </is>
       </c>
-      <c r="AQ49" s="3" t="inlineStr"/>
+      <c r="AR49" s="3" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
@@ -9734,22 +9979,27 @@
           <t>Non-UK</t>
         </is>
       </c>
-      <c r="AL50" s="3" t="b">
+      <c r="AL50" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM50" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="AM50" s="3" t="inlineStr">
+      <c r="AN50" s="3" t="inlineStr">
         <is>
           <t>No Action</t>
         </is>
       </c>
-      <c r="AN50" s="3" t="n"/>
-      <c r="AO50" s="4" t="inlineStr"/>
-      <c r="AP50" s="4" t="inlineStr">
+      <c r="AO50" s="3" t="n"/>
+      <c r="AP50" s="4" t="inlineStr"/>
+      <c r="AQ50" s="4" t="inlineStr">
         <is>
           <t>Stage 'In Conversation' is on the do-not-message list - no message drafted, no assumptions made about prior conversation content.</t>
         </is>
       </c>
-      <c r="AQ50" s="3" t="inlineStr"/>
+      <c r="AR50" s="3" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
@@ -9915,26 +10165,31 @@
           <t>Missing Contact; Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL51" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM51" s="3" t="inlineStr">
+      <c r="AL51" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM51" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN51" s="3" t="inlineStr">
         <is>
           <t>Cold</t>
         </is>
       </c>
-      <c r="AN51" s="3" t="n"/>
-      <c r="AO51" s="4" t="inlineStr">
+      <c r="AO51" s="3" t="n"/>
+      <c r="AP51" s="4" t="inlineStr">
         <is>
           <t>Hi there, I came across your shop and noticed your live-sale format on Whatnot. I work with Fleek, a wholesale marketplace connecting retailers and resellers with inventory from trusted suppliers and brands. Would it be useful to see what's currently available that fits what you stock?</t>
         </is>
       </c>
-      <c r="AP51" s="4" t="inlineStr">
+      <c r="AQ51" s="4" t="inlineStr">
         <is>
           <t>Stage identified as New Lead (Cold). Personalisation drawn from notes: your live-sale format on Whatnot. No prior contact on record - treated as first outreach.</t>
         </is>
       </c>
-      <c r="AQ51" s="3" t="inlineStr">
+      <c r="AR51" s="3" t="inlineStr">
         <is>
           <t>your live-sale format on Whatnot</t>
         </is>
@@ -10104,26 +10359,31 @@
           <t>None</t>
         </is>
       </c>
-      <c r="AL52" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM52" s="3" t="inlineStr">
+      <c r="AL52" s="3" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="AM52" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN52" s="3" t="inlineStr">
         <is>
           <t>Customer Check-In</t>
         </is>
       </c>
-      <c r="AN52" s="3" t="n"/>
-      <c r="AO52" s="4" t="inlineStr">
+      <c r="AO52" s="3" t="n"/>
+      <c r="AP52" s="4" t="inlineStr">
         <is>
           <t>Hi Chloe, wanted to check in properly rather than send a generic update, given the Y2K and grunge one-offs you carry. Keen to hear how things have been going and whether there's anything new worth exploring together. Any gaps in what you're sourcing at the moment, or new ranges you're thinking about?</t>
         </is>
       </c>
-      <c r="AP52" s="4" t="inlineStr">
+      <c r="AQ52" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Closed Won (Customer Check-In). Personalisation drawn from notes: your Y2K, grunge and reworked one-off pieces. Last contacted 29 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ52" s="3" t="inlineStr">
+      <c r="AR52" s="3" t="inlineStr">
         <is>
           <t>your Y2K, grunge and reworked one-off pieces</t>
         </is>
@@ -10293,26 +10553,31 @@
           <t>Missing Website</t>
         </is>
       </c>
-      <c r="AL53" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM53" s="3" t="inlineStr">
+      <c r="AL53" s="3" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="AM53" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN53" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN53" s="3" t="n"/>
-      <c r="AO53" s="4" t="inlineStr">
+      <c r="AO53" s="3" t="n"/>
+      <c r="AP53" s="4" t="inlineStr">
         <is>
           <t>Hi Ben, it's been a little while, so wanted to check back in given your hand-picked edit spanning the 60s through the 90s. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Good to put a name to the shop after meeting at the market - still keen to swing by. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP53" s="4" t="inlineStr">
+      <c r="AQ53" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Demo Booked (Re-Engagement). Personalisation drawn from notes: your hand-picked edit spanning the 60s through the 90s. Notes flagged a specific objection/context, addressed directly rather than ignored. Last contacted 31 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ53" s="3" t="inlineStr">
+      <c r="AR53" s="3" t="inlineStr">
         <is>
           <t>your hand-picked edit spanning the 60s through the 90s</t>
         </is>
@@ -10482,26 +10747,31 @@
           <t>None</t>
         </is>
       </c>
-      <c r="AL54" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM54" s="3" t="inlineStr">
+      <c r="AL54" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM54" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN54" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN54" s="3" t="n"/>
-      <c r="AO54" s="4" t="inlineStr">
+      <c r="AO54" s="3" t="n"/>
+      <c r="AP54" s="4" t="inlineStr">
         <is>
           <t>Hi James, it's been a little while, so wanted to check back in given your retro football shirt and vintage sportswear range. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. No worries on the missed callback - happy to try again whenever suits. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP54" s="4" t="inlineStr">
+      <c r="AQ54" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Contacted (Re-Engagement). Personalisation drawn from notes: your retro football shirt and vintage sportswear range. Notes flagged a specific objection/context, addressed directly rather than ignored. Last contacted 39 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ54" s="3" t="inlineStr">
+      <c r="AR54" s="3" t="inlineStr">
         <is>
           <t>your retro football shirt and vintage sportswear range</t>
         </is>
@@ -10671,26 +10941,31 @@
           <t>Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL55" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM55" s="3" t="inlineStr">
+      <c r="AL55" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM55" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN55" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN55" s="3" t="n"/>
-      <c r="AO55" s="4" t="inlineStr">
+      <c r="AO55" s="3" t="n"/>
+      <c r="AP55" s="4" t="inlineStr">
         <is>
           <t>Hi there, it's been a little while, so wanted to check back in given running your shop straight through Instagram DMs. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP55" s="4" t="inlineStr">
+      <c r="AQ55" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Replied (Re-Engagement). Personalisation drawn from notes: running your shop straight through Instagram DMs. Last contacted 92 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ55" s="3" t="inlineStr">
+      <c r="AR55" s="3" t="inlineStr">
         <is>
           <t>running your shop straight through Instagram DMs</t>
         </is>
@@ -10860,26 +11135,31 @@
           <t>None</t>
         </is>
       </c>
-      <c r="AL56" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM56" s="3" t="inlineStr">
+      <c r="AL56" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM56" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN56" s="3" t="inlineStr">
         <is>
           <t>Churned-Win-Back</t>
         </is>
       </c>
-      <c r="AN56" s="3" t="n"/>
-      <c r="AO56" s="4" t="inlineStr">
+      <c r="AO56" s="3" t="n"/>
+      <c r="AP56" s="4" t="inlineStr">
         <is>
           <t>Hi Sam, it's been a while since we last worked together, so wanted to reach out honestly rather than pretend nothing's changed. Given your market stall, I understand if the timing wasn't right before. Would it be worth a low-pressure conversation about what's changed on our side, in case it's relevant again?</t>
         </is>
       </c>
-      <c r="AP56" s="4" t="inlineStr">
+      <c r="AQ56" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Churned (Churned-Win-Back). Personalisation drawn from category (notes unavailable): your market stall setup. Last contacted 68 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ56" s="3" t="inlineStr">
+      <c r="AR56" s="3" t="inlineStr">
         <is>
           <t>your market stall setup</t>
         </is>
@@ -11049,26 +11329,31 @@
           <t>Missing Contact; Missing Website</t>
         </is>
       </c>
-      <c r="AL57" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM57" s="3" t="inlineStr">
+      <c r="AL57" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM57" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN57" s="3" t="inlineStr">
         <is>
           <t>Churned-Win-Back</t>
         </is>
       </c>
-      <c r="AN57" s="3" t="n"/>
-      <c r="AO57" s="4" t="inlineStr">
+      <c r="AO57" s="3" t="n"/>
+      <c r="AP57" s="4" t="inlineStr">
         <is>
           <t>Hi Sofia, it's been a while since we last worked together, so wanted to reach out honestly rather than pretend nothing's changed. Given the decades-spanning edit you've hand-picked, I understand if the timing wasn't right before. Would it be worth a low-pressure conversation about what's changed on our side, in case it's relevant again?</t>
         </is>
       </c>
-      <c r="AP57" s="4" t="inlineStr">
+      <c r="AQ57" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Dormant (Churned-Win-Back). Personalisation drawn from notes: your hand-picked edit spanning the 60s through the 90s. Last contacted 74 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ57" s="3" t="inlineStr">
+      <c r="AR57" s="3" t="inlineStr">
         <is>
           <t>your hand-picked edit spanning the 60s through the 90s</t>
         </is>
@@ -11238,26 +11523,31 @@
           <t>Missing Contact; Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL58" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM58" s="3" t="inlineStr">
+      <c r="AL58" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM58" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN58" s="3" t="inlineStr">
         <is>
           <t>Cold</t>
         </is>
       </c>
-      <c r="AN58" s="3" t="n"/>
-      <c r="AO58" s="4" t="inlineStr">
+      <c r="AO58" s="3" t="n"/>
+      <c r="AP58" s="4" t="inlineStr">
         <is>
           <t>Hi there, I came across your shop and noticed how quickly your stock turns over. I work with Fleek, a wholesale marketplace connecting retailers and resellers with inventory from trusted suppliers and brands. Would it be useful to see what's currently available that fits what you stock?</t>
         </is>
       </c>
-      <c r="AP58" s="4" t="inlineStr">
+      <c r="AQ58" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Contacted (Cold). Personalisation drawn from notes: how quickly your stock turns over. Last contacted 17 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ58" s="3" t="inlineStr">
+      <c r="AR58" s="3" t="inlineStr">
         <is>
           <t>how quickly your stock turns over</t>
         </is>
@@ -11427,26 +11717,31 @@
           <t>None</t>
         </is>
       </c>
-      <c r="AL59" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM59" s="3" t="inlineStr">
+      <c r="AL59" s="3" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="AM59" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN59" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN59" s="3" t="n"/>
-      <c r="AO59" s="4" t="inlineStr">
+      <c r="AO59" s="3" t="n"/>
+      <c r="AP59" s="4" t="inlineStr">
         <is>
           <t>Hi there, it's been a little while, so wanted to check back in given your hand-picked edit spanning the 60s through the 90s. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP59" s="4" t="inlineStr">
+      <c r="AQ59" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Replied (Re-Engagement). Personalisation drawn from notes: your hand-picked edit spanning the 60s through the 90s. Last contacted 30 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ59" s="3" t="inlineStr">
+      <c r="AR59" s="3" t="inlineStr">
         <is>
           <t>your hand-picked edit spanning the 60s through the 90s</t>
         </is>
@@ -11616,26 +11911,31 @@
           <t>Missing Contact; Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL60" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM60" s="3" t="inlineStr">
+      <c r="AL60" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM60" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN60" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN60" s="3" t="n"/>
-      <c r="AO60" s="4" t="inlineStr">
+      <c r="AO60" s="3" t="n"/>
+      <c r="AP60" s="4" t="inlineStr">
         <is>
           <t>Hi there, it's been a little while, so wanted to check back in given how quickly your stock turns over. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP60" s="4" t="inlineStr">
+      <c r="AQ60" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Replied (Re-Engagement). Personalisation drawn from notes: how quickly your stock turns over. Last contacted 59 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ60" s="3" t="inlineStr">
+      <c r="AR60" s="3" t="inlineStr">
         <is>
           <t>how quickly your stock turns over</t>
         </is>
@@ -11805,26 +12105,31 @@
           <t>Missing Contact; Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL61" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM61" s="3" t="inlineStr">
+      <c r="AL61" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM61" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN61" s="3" t="inlineStr">
         <is>
           <t>Cold</t>
         </is>
       </c>
-      <c r="AN61" s="3" t="n"/>
-      <c r="AO61" s="4" t="inlineStr">
+      <c r="AO61" s="3" t="n"/>
+      <c r="AP61" s="4" t="inlineStr">
         <is>
           <t>Hi there, I came across your shop and noticed selling through Depop. I work with Fleek, a wholesale marketplace connecting retailers and resellers with inventory from trusted suppliers and brands. Would it be useful to see what's currently available that fits what you stock?</t>
         </is>
       </c>
-      <c r="AP61" s="4" t="inlineStr">
+      <c r="AQ61" s="4" t="inlineStr">
         <is>
           <t>Stage identified as New Lead (Cold). Personalisation drawn from channel (notes unavailable): selling through Depop. No prior contact on record - treated as first outreach.</t>
         </is>
       </c>
-      <c r="AQ61" s="3" t="inlineStr">
+      <c r="AR61" s="3" t="inlineStr">
         <is>
           <t>selling through Depop</t>
         </is>
@@ -11994,26 +12299,31 @@
           <t>None</t>
         </is>
       </c>
-      <c r="AL62" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM62" s="3" t="inlineStr">
+      <c r="AL62" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM62" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN62" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN62" s="3" t="n"/>
-      <c r="AO62" s="4" t="inlineStr">
+      <c r="AO62" s="3" t="n"/>
+      <c r="AP62" s="4" t="inlineStr">
         <is>
           <t>Hi Leo, it's been a little while, so wanted to check back in given your Y2K, grunge and reworked one-off pieces. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Happy to work around your weekend trade - midweek suits us fine. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP62" s="4" t="inlineStr">
+      <c r="AQ62" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Contacted (Re-Engagement). Personalisation drawn from notes: your Y2K, grunge and reworked one-off pieces. Notes flagged a specific objection/context, addressed directly rather than ignored. Last contacted 39 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ62" s="3" t="inlineStr">
+      <c r="AR62" s="3" t="inlineStr">
         <is>
           <t>your Y2K, grunge and reworked one-off pieces</t>
         </is>
@@ -12183,26 +12493,31 @@
           <t>Missing Contact; Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL63" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM63" s="3" t="inlineStr">
+      <c r="AL63" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM63" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN63" s="3" t="inlineStr">
         <is>
           <t>Inbound</t>
         </is>
       </c>
-      <c r="AN63" s="3" t="n"/>
-      <c r="AO63" s="4" t="inlineStr">
+      <c r="AO63" s="3" t="n"/>
+      <c r="AP63" s="4" t="inlineStr">
         <is>
           <t>Hi there, thanks for getting in touch - I had a look at selling across both Depop and Vinted before writing back. Fleek connects shops like yours with inventory from trusted suppliers, so given your presence across both Depop and Vinted, it seemed worth a proper reply rather than a generic one. What's the main gap in sourcing right now - more volume, more variety, or something specific you're struggling to find?</t>
         </is>
       </c>
-      <c r="AP63" s="4" t="inlineStr">
+      <c r="AQ63" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Inbound (Inbound). Personalisation drawn from notes: selling across both Depop and Vinted. No prior contact on record - treated as first outreach.</t>
         </is>
       </c>
-      <c r="AQ63" s="3" t="inlineStr">
+      <c r="AR63" s="3" t="inlineStr">
         <is>
           <t>selling across both Depop and Vinted</t>
         </is>
@@ -12372,26 +12687,31 @@
           <t>None</t>
         </is>
       </c>
-      <c r="AL64" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM64" s="3" t="inlineStr">
+      <c r="AL64" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM64" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN64" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN64" s="3" t="n"/>
-      <c r="AO64" s="4" t="inlineStr">
+      <c r="AO64" s="3" t="n"/>
+      <c r="AP64" s="4" t="inlineStr">
         <is>
           <t>Hi Tom, it's been a little while, so wanted to check back in given your 80s/90s denim and sportswear edit. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. The sizing-mix issue from 2023 was a fair complaint, and the way we curate mixes has changed since - genuinely curious whether it's worth a second look. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP64" s="4" t="inlineStr">
+      <c r="AQ64" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Negotiating (Re-Engagement). Personalisation drawn from notes: your 80s/90s denim and sportswear edit. Notes flagged a specific objection/context, addressed directly rather than ignored. Last contacted 43 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ64" s="3" t="inlineStr">
+      <c r="AR64" s="3" t="inlineStr">
         <is>
           <t>your 80s/90s denim and sportswear edit</t>
         </is>
@@ -12561,26 +12881,31 @@
           <t>Missing Website</t>
         </is>
       </c>
-      <c r="AL65" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM65" s="3" t="inlineStr">
+      <c r="AL65" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM65" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN65" s="3" t="inlineStr">
         <is>
           <t>Cold</t>
         </is>
       </c>
-      <c r="AN65" s="3" t="n"/>
-      <c r="AO65" s="4" t="inlineStr">
+      <c r="AO65" s="3" t="n"/>
+      <c r="AP65" s="4" t="inlineStr">
         <is>
           <t>Hi there, I came across your shop and noticed your retro football shirt and vintage sportswear range. I work with Fleek, a wholesale marketplace connecting retailers and resellers with inventory from trusted suppliers and brands. Would it be useful to see what's currently available that fits what you stock?</t>
         </is>
       </c>
-      <c r="AP65" s="4" t="inlineStr">
+      <c r="AQ65" s="4" t="inlineStr">
         <is>
           <t>Stage identified as New Lead (Cold). Personalisation drawn from notes: your retro football shirt and vintage sportswear range. No prior contact on record - treated as first outreach.</t>
         </is>
       </c>
-      <c r="AQ65" s="3" t="inlineStr">
+      <c r="AR65" s="3" t="inlineStr">
         <is>
           <t>your retro football shirt and vintage sportswear range</t>
         </is>
@@ -12750,26 +13075,31 @@
           <t>Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL66" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM66" s="3" t="inlineStr">
+      <c r="AL66" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM66" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN66" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN66" s="3" t="n"/>
-      <c r="AO66" s="4" t="inlineStr">
+      <c r="AO66" s="3" t="n"/>
+      <c r="AP66" s="4" t="inlineStr">
         <is>
           <t>Hi there, it's been a little while, so wanted to check back in given how quickly your stock turns over. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP66" s="4" t="inlineStr">
+      <c r="AQ66" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Replied (Re-Engagement). Personalisation drawn from notes: how quickly your stock turns over. Last contacted 21 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ66" s="3" t="inlineStr">
+      <c r="AR66" s="3" t="inlineStr">
         <is>
           <t>how quickly your stock turns over</t>
         </is>
@@ -12939,26 +13269,31 @@
           <t>Missing Contact; Missing Website; Non-UK</t>
         </is>
       </c>
-      <c r="AL67" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM67" s="3" t="inlineStr">
+      <c r="AL67" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM67" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN67" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN67" s="3" t="n"/>
-      <c r="AO67" s="4" t="inlineStr">
+      <c r="AO67" s="3" t="n"/>
+      <c r="AP67" s="4" t="inlineStr">
         <is>
           <t>Hi there, it's been a little while, so wanted to check back in given your retro football shirt and vintage sportswear range. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP67" s="4" t="inlineStr">
+      <c r="AQ67" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Contacted (Re-Engagement). Personalisation drawn from notes: your retro football shirt and vintage sportswear range. Last contacted 29 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ67" s="3" t="inlineStr">
+      <c r="AR67" s="3" t="inlineStr">
         <is>
           <t>your retro football shirt and vintage sportswear range</t>
         </is>
@@ -13128,26 +13463,31 @@
           <t>Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL68" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM68" s="3" t="inlineStr">
+      <c r="AL68" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM68" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN68" s="3" t="inlineStr">
         <is>
           <t>Churned-Win-Back</t>
         </is>
       </c>
-      <c r="AN68" s="3" t="n"/>
-      <c r="AO68" s="4" t="inlineStr">
+      <c r="AO68" s="3" t="n"/>
+      <c r="AP68" s="4" t="inlineStr">
         <is>
           <t>Hi there, it's been a while since we last worked together, so wanted to reach out honestly rather than pretend nothing's changed. Given your Vinted shop, I understand if the timing wasn't right before. Would it be worth a low-pressure conversation about what's changed on our side, in case it's relevant again?</t>
         </is>
       </c>
-      <c r="AP68" s="4" t="inlineStr">
+      <c r="AQ68" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Churned (Churned-Win-Back). Personalisation drawn from channel (notes unavailable): selling through Vinted. Last contacted 43 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ68" s="3" t="inlineStr">
+      <c r="AR68" s="3" t="inlineStr">
         <is>
           <t>selling through Vinted</t>
         </is>
@@ -13317,26 +13657,31 @@
           <t>Missing Contact; Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL69" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM69" s="3" t="inlineStr">
+      <c r="AL69" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM69" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN69" s="3" t="inlineStr">
         <is>
           <t>Cold</t>
         </is>
       </c>
-      <c r="AN69" s="3" t="n"/>
-      <c r="AO69" s="4" t="inlineStr">
+      <c r="AO69" s="3" t="n"/>
+      <c r="AP69" s="4" t="inlineStr">
         <is>
           <t>Hi there, I came across your shop and noticed selling through Depop. I work with Fleek, a wholesale marketplace connecting retailers and resellers with inventory from trusted suppliers and brands. Would it be useful to see what's currently available that fits what you stock?</t>
         </is>
       </c>
-      <c r="AP69" s="4" t="inlineStr">
+      <c r="AQ69" s="4" t="inlineStr">
         <is>
           <t>Stage identified as New Lead (Cold). Personalisation drawn from channel (notes unavailable): selling through Depop. No prior contact on record - treated as first outreach.</t>
         </is>
       </c>
-      <c r="AQ69" s="3" t="inlineStr">
+      <c r="AR69" s="3" t="inlineStr">
         <is>
           <t>selling through Depop</t>
         </is>
@@ -13506,26 +13851,31 @@
           <t>None</t>
         </is>
       </c>
-      <c r="AL70" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM70" s="3" t="inlineStr">
+      <c r="AL70" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM70" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN70" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN70" s="3" t="n"/>
-      <c r="AO70" s="4" t="inlineStr">
+      <c r="AO70" s="3" t="n"/>
+      <c r="AP70" s="4" t="inlineStr">
         <is>
           <t>Hi there, it's been a little while, so wanted to check back in given your Y2K, grunge and reworked one-off pieces. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP70" s="4" t="inlineStr">
+      <c r="AQ70" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Contacted (Re-Engagement). Personalisation drawn from notes: your Y2K, grunge and reworked one-off pieces. Last contacted 85 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ70" s="3" t="inlineStr">
+      <c r="AR70" s="3" t="inlineStr">
         <is>
           <t>your Y2K, grunge and reworked one-off pieces</t>
         </is>
@@ -13695,26 +14045,31 @@
           <t>None</t>
         </is>
       </c>
-      <c r="AL71" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM71" s="3" t="inlineStr">
+      <c r="AL71" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM71" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN71" s="3" t="inlineStr">
         <is>
           <t>Churned-Win-Back</t>
         </is>
       </c>
-      <c r="AN71" s="3" t="n"/>
-      <c r="AO71" s="4" t="inlineStr">
+      <c r="AO71" s="3" t="n"/>
+      <c r="AP71" s="4" t="inlineStr">
         <is>
           <t>Hi there, it's been a while since we last worked together, so wanted to reach out honestly rather than pretend nothing's changed. Given the 80s/90s denim and sportswear range you've built, I understand if the timing wasn't right before. Would it be worth a low-pressure conversation about what's changed on our side, in case it's relevant again?</t>
         </is>
       </c>
-      <c r="AP71" s="4" t="inlineStr">
+      <c r="AQ71" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Churned (Churned-Win-Back). Personalisation drawn from notes: your 80s/90s denim and sportswear edit. Last contacted 57 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ71" s="3" t="inlineStr">
+      <c r="AR71" s="3" t="inlineStr">
         <is>
           <t>your 80s/90s denim and sportswear edit</t>
         </is>
@@ -13884,26 +14239,31 @@
           <t>Multiple Websites</t>
         </is>
       </c>
-      <c r="AL72" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM72" s="3" t="inlineStr">
+      <c r="AL72" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM72" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN72" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN72" s="3" t="n"/>
-      <c r="AO72" s="4" t="inlineStr">
+      <c r="AO72" s="3" t="n"/>
+      <c r="AP72" s="4" t="inlineStr">
         <is>
           <t>Hi there, it's been a little while, so wanted to check back in given your reworked and archive designer pieces. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP72" s="4" t="inlineStr">
+      <c r="AQ72" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Contacted (Re-Engagement). Personalisation drawn from notes: your reworked and archive designer pieces. Last contacted 31 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ72" s="3" t="inlineStr">
+      <c r="AR72" s="3" t="inlineStr">
         <is>
           <t>your reworked and archive designer pieces</t>
         </is>
@@ -14073,26 +14433,31 @@
           <t>Non-UK</t>
         </is>
       </c>
-      <c r="AL73" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM73" s="3" t="inlineStr">
+      <c r="AL73" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM73" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN73" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN73" s="3" t="n"/>
-      <c r="AO73" s="4" t="inlineStr">
+      <c r="AO73" s="3" t="n"/>
+      <c r="AP73" s="4" t="inlineStr">
         <is>
           <t>Hi there, it's been a little while, so wanted to check back in given your reworked and archive designer pieces. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP73" s="4" t="inlineStr">
+      <c r="AQ73" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Contacted (Re-Engagement). Personalisation drawn from notes: your reworked and archive designer pieces. Last contacted 42 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ73" s="3" t="inlineStr">
+      <c r="AR73" s="3" t="inlineStr">
         <is>
           <t>your reworked and archive designer pieces</t>
         </is>
@@ -14262,26 +14627,31 @@
           <t>Missing Contact; Missing Website</t>
         </is>
       </c>
-      <c r="AL74" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM74" s="3" t="inlineStr">
+      <c r="AL74" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM74" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN74" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN74" s="3" t="n"/>
-      <c r="AO74" s="4" t="inlineStr">
+      <c r="AO74" s="3" t="n"/>
+      <c r="AP74" s="4" t="inlineStr">
         <is>
           <t>Hi Mila, it's been a little while, so wanted to check back in given your 80s/90s denim and sportswear edit. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP74" s="4" t="inlineStr">
+      <c r="AQ74" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Contacted (Re-Engagement). Personalisation drawn from notes: your 80s/90s denim and sportswear edit. Last contacted 39 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ74" s="3" t="inlineStr">
+      <c r="AR74" s="3" t="inlineStr">
         <is>
           <t>your 80s/90s denim and sportswear edit</t>
         </is>
@@ -14451,26 +14821,31 @@
           <t>Missing Website</t>
         </is>
       </c>
-      <c r="AL75" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM75" s="3" t="inlineStr">
+      <c r="AL75" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM75" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN75" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN75" s="3" t="n"/>
-      <c r="AO75" s="4" t="inlineStr">
+      <c r="AO75" s="3" t="n"/>
+      <c r="AP75" s="4" t="inlineStr">
         <is>
           <t>Hi Leo, it's been a little while, so wanted to check back in given your hand-picked edit spanning the 60s through the 90s. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP75" s="4" t="inlineStr">
+      <c r="AQ75" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Contacted (Re-Engagement). Personalisation drawn from notes: your hand-picked edit spanning the 60s through the 90s. Last contacted 123 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ75" s="3" t="inlineStr">
+      <c r="AR75" s="3" t="inlineStr">
         <is>
           <t>your hand-picked edit spanning the 60s through the 90s</t>
         </is>
@@ -14640,26 +15015,31 @@
           <t>None</t>
         </is>
       </c>
-      <c r="AL76" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM76" s="3" t="inlineStr">
+      <c r="AL76" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM76" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN76" s="3" t="inlineStr">
         <is>
           <t>Cold</t>
         </is>
       </c>
-      <c r="AN76" s="3" t="n"/>
-      <c r="AO76" s="4" t="inlineStr">
+      <c r="AO76" s="3" t="n"/>
+      <c r="AP76" s="4" t="inlineStr">
         <is>
           <t>Hi there, I came across your shop and noticed your reworked and archive designer pieces. I work with Fleek, a wholesale marketplace connecting retailers and resellers with inventory from trusted suppliers and brands. Worth a quick correction on that: we work with shops at a range of sizes, not just small resellers - happy to show you what that actually looks like. Would it be useful to see what's currently available that fits what you stock?</t>
         </is>
       </c>
-      <c r="AP76" s="4" t="inlineStr">
+      <c r="AQ76" s="4" t="inlineStr">
         <is>
           <t>Stage identified as New Lead (Cold). Personalisation drawn from notes: your reworked and archive designer pieces. Notes flagged a specific objection/context, addressed directly rather than ignored. No prior contact on record - treated as first outreach.</t>
         </is>
       </c>
-      <c r="AQ76" s="3" t="inlineStr">
+      <c r="AR76" s="3" t="inlineStr">
         <is>
           <t>your reworked and archive designer pieces</t>
         </is>
@@ -14829,26 +15209,31 @@
           <t>Missing Contact; Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL77" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM77" s="3" t="inlineStr">
+      <c r="AL77" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM77" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN77" s="3" t="inlineStr">
         <is>
           <t>Cold</t>
         </is>
       </c>
-      <c r="AN77" s="3" t="n"/>
-      <c r="AO77" s="4" t="inlineStr">
+      <c r="AO77" s="3" t="n"/>
+      <c r="AP77" s="4" t="inlineStr">
         <is>
           <t>Hi there, I came across your shop and noticed your live-sale format on Whatnot. I work with Fleek, a wholesale marketplace connecting retailers and resellers with inventory from trusted suppliers and brands. Would it be useful to see what's currently available that fits what you stock?</t>
         </is>
       </c>
-      <c r="AP77" s="4" t="inlineStr">
+      <c r="AQ77" s="4" t="inlineStr">
         <is>
           <t>Stage identified as New Lead (Cold). Personalisation drawn from notes: your live-sale format on Whatnot. No prior contact on record - treated as first outreach.</t>
         </is>
       </c>
-      <c r="AQ77" s="3" t="inlineStr">
+      <c r="AR77" s="3" t="inlineStr">
         <is>
           <t>your live-sale format on Whatnot</t>
         </is>
@@ -15018,22 +15403,27 @@
           <t>Missing Instagram</t>
         </is>
       </c>
-      <c r="AL78" s="3" t="b">
+      <c r="AL78" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM78" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="AM78" s="3" t="inlineStr">
+      <c r="AN78" s="3" t="inlineStr">
         <is>
           <t>No Action</t>
         </is>
       </c>
-      <c r="AN78" s="3" t="n"/>
-      <c r="AO78" s="4" t="inlineStr"/>
-      <c r="AP78" s="4" t="inlineStr">
+      <c r="AO78" s="3" t="n"/>
+      <c r="AP78" s="4" t="inlineStr"/>
+      <c r="AQ78" s="4" t="inlineStr">
         <is>
           <t>Stage 'Not Interested' is on the do-not-message list - no message drafted, no assumptions made about prior conversation content.</t>
         </is>
       </c>
-      <c r="AQ78" s="3" t="inlineStr"/>
+      <c r="AR78" s="3" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
@@ -15199,26 +15589,31 @@
           <t>None</t>
         </is>
       </c>
-      <c r="AL79" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM79" s="3" t="inlineStr">
+      <c r="AL79" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM79" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN79" s="3" t="inlineStr">
         <is>
           <t>Cold</t>
         </is>
       </c>
-      <c r="AN79" s="3" t="n"/>
-      <c r="AO79" s="4" t="inlineStr">
+      <c r="AO79" s="3" t="n"/>
+      <c r="AP79" s="4" t="inlineStr">
         <is>
           <t>Hi there, I came across your shop and noticed your market stall setup. I work with Fleek, a wholesale marketplace connecting retailers and resellers with inventory from trusted suppliers and brands. Would it be useful to see what's currently available that fits what you stock?</t>
         </is>
       </c>
-      <c r="AP79" s="4" t="inlineStr">
+      <c r="AQ79" s="4" t="inlineStr">
         <is>
           <t>Stage identified as New Lead (Cold). Personalisation drawn from category (notes unavailable): your market stall setup. No prior contact on record - treated as first outreach.</t>
         </is>
       </c>
-      <c r="AQ79" s="3" t="inlineStr">
+      <c r="AR79" s="3" t="inlineStr">
         <is>
           <t>your market stall setup</t>
         </is>
@@ -15388,27 +15783,32 @@
           <t>Missing Website; Non-UK</t>
         </is>
       </c>
-      <c r="AL80" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM80" s="3" t="inlineStr">
+      <c r="AL80" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM80" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN80" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN80" s="3" t="n"/>
-      <c r="AO80" s="4" t="inlineStr">
+      <c r="AO80" s="3" t="n"/>
+      <c r="AP80" s="4" t="inlineStr">
         <is>
           <t>English: Hi Priya, it's been a little while, so wanted to check back in given your curated womenswear built around Levi's and band tees. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Makes sense to see it in action first - I can walk you through the app directly rather than describe it. Worth a quick chat to see where things stand?
 Translated (French): Bonjour Priya, cela fait un moment, je voulais donc reprendre contact étant donné votre sélection femme construite autour de Levi's et de t-shirts de groupes de musique. Aucune pression si le moment n'est plus idéal, mais si l'approvisionnement reste d'actualité, je serais ravi d'en reparler. Voir l'application avant de vous engager est tout à fait logique - je peux vous la présenter directement plutôt que de la décrire. Cela vaudrait-il la peine d'en discuter rapidement ?</t>
         </is>
       </c>
-      <c r="AP80" s="4" t="inlineStr">
+      <c r="AQ80" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Visit Booked (Re-Engagement). Personalisation drawn from notes: your curated womenswear built around Levi's and band tees. Notes flagged a specific objection/context, addressed directly rather than ignored. Last contacted 56 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ80" s="3" t="inlineStr">
+      <c r="AR80" s="3" t="inlineStr">
         <is>
           <t>your curated womenswear built around Levi's and band tees</t>
         </is>
@@ -15578,26 +15978,31 @@
           <t>Missing Instagram</t>
         </is>
       </c>
-      <c r="AL81" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM81" s="3" t="inlineStr">
+      <c r="AL81" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM81" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN81" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN81" s="3" t="n"/>
-      <c r="AO81" s="4" t="inlineStr">
+      <c r="AO81" s="3" t="n"/>
+      <c r="AP81" s="4" t="inlineStr">
         <is>
           <t>Hi Nadia, it's been a little while, so wanted to check back in given your hand-picked edit spanning the 60s through the 90s. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP81" s="4" t="inlineStr">
+      <c r="AQ81" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Contacted (Re-Engagement). Personalisation drawn from notes: your hand-picked edit spanning the 60s through the 90s. Last contacted 126 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ81" s="3" t="inlineStr">
+      <c r="AR81" s="3" t="inlineStr">
         <is>
           <t>your hand-picked edit spanning the 60s through the 90s</t>
         </is>
@@ -15767,26 +16172,31 @@
           <t>Non-UK</t>
         </is>
       </c>
-      <c r="AL82" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM82" s="3" t="inlineStr">
+      <c r="AL82" s="3" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="AM82" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN82" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN82" s="3" t="n"/>
-      <c r="AO82" s="4" t="inlineStr">
+      <c r="AO82" s="3" t="n"/>
+      <c r="AP82" s="4" t="inlineStr">
         <is>
           <t>Hi Priya, it's been a little while, so wanted to check back in given your curated womenswear built around Levi's and band tees. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Since email hasn't been landing, DMs are probably the easier way to reach you. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP82" s="4" t="inlineStr">
+      <c r="AQ82" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Visit Booked (Re-Engagement). Personalisation drawn from notes: your curated womenswear built around Levi's and band tees. Notes flagged a specific objection/context, addressed directly rather than ignored. Last contacted 34 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ82" s="3" t="inlineStr">
+      <c r="AR82" s="3" t="inlineStr">
         <is>
           <t>your curated womenswear built around Levi's and band tees</t>
         </is>
@@ -15956,26 +16366,31 @@
           <t>Missing Contact; Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL83" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM83" s="3" t="inlineStr">
+      <c r="AL83" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM83" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN83" s="3" t="inlineStr">
         <is>
           <t>Cold</t>
         </is>
       </c>
-      <c r="AN83" s="3" t="n"/>
-      <c r="AO83" s="4" t="inlineStr">
+      <c r="AO83" s="3" t="n"/>
+      <c r="AP83" s="4" t="inlineStr">
         <is>
           <t>Hi there, I came across your shop and noticed how quickly your stock turns over. I work with Fleek, a wholesale marketplace connecting retailers and resellers with inventory from trusted suppliers and brands. Would it be useful to see what's currently available that fits what you stock?</t>
         </is>
       </c>
-      <c r="AP83" s="4" t="inlineStr">
+      <c r="AQ83" s="4" t="inlineStr">
         <is>
           <t>Stage identified as New Lead (Cold). Personalisation drawn from notes: how quickly your stock turns over. No prior contact on record - treated as first outreach.</t>
         </is>
       </c>
-      <c r="AQ83" s="3" t="inlineStr">
+      <c r="AR83" s="3" t="inlineStr">
         <is>
           <t>how quickly your stock turns over</t>
         </is>
@@ -16145,26 +16560,31 @@
           <t>Missing Contact; Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL84" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM84" s="3" t="inlineStr">
+      <c r="AL84" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM84" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN84" s="3" t="inlineStr">
         <is>
           <t>Customer Check-In</t>
         </is>
       </c>
-      <c r="AN84" s="3" t="n"/>
-      <c r="AO84" s="4" t="inlineStr">
+      <c r="AO84" s="3" t="n"/>
+      <c r="AP84" s="4" t="inlineStr">
         <is>
           <t>Hi there, wanted to check in properly rather than send a generic update, given the DM-led way you run sales. Keen to hear how things have been going and whether there's anything new worth exploring together. Any gaps in what you're sourcing at the moment, or new ranges you're thinking about?</t>
         </is>
       </c>
-      <c r="AP84" s="4" t="inlineStr">
+      <c r="AQ84" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Closed Won (Customer Check-In). Personalisation drawn from notes: running your shop straight through Instagram DMs. Last contacted 16 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ84" s="3" t="inlineStr">
+      <c r="AR84" s="3" t="inlineStr">
         <is>
           <t>running your shop straight through Instagram DMs</t>
         </is>
@@ -16334,26 +16754,31 @@
           <t>Possible Duplicate - Unverified</t>
         </is>
       </c>
-      <c r="AL85" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM85" s="5" t="inlineStr">
+      <c r="AL85" s="5" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM85" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN85" s="5" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN85" s="5" t="n"/>
-      <c r="AO85" s="6" t="inlineStr">
+      <c r="AO85" s="5" t="n"/>
+      <c r="AP85" s="6" t="inlineStr">
         <is>
           <t>Hi Chloe, it's been a little while, so wanted to check back in given your retro football shirt and vintage sportswear range. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP85" s="6" t="inlineStr">
+      <c r="AQ85" s="6" t="inlineStr">
         <is>
           <t>Stage identified as Replied (Re-Engagement). Personalisation drawn from notes: your retro football shirt and vintage sportswear range. Last contacted 22 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ85" s="5" t="inlineStr">
+      <c r="AR85" s="5" t="inlineStr">
         <is>
           <t>your retro football shirt and vintage sportswear range</t>
         </is>
@@ -16523,26 +16948,31 @@
           <t>Missing Website; Missing Instagram</t>
         </is>
       </c>
-      <c r="AL86" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM86" s="3" t="inlineStr">
+      <c r="AL86" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM86" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN86" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN86" s="3" t="n"/>
-      <c r="AO86" s="4" t="inlineStr">
+      <c r="AO86" s="3" t="n"/>
+      <c r="AP86" s="4" t="inlineStr">
         <is>
           <t>Hi Freya, it's been a little while, so wanted to check back in given your workwear and military surplus range, including Carhartt. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP86" s="4" t="inlineStr">
+      <c r="AQ86" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Quote Sent (Re-Engagement). Personalisation drawn from notes: your workwear and military surplus range, including Carhartt. Last contacted 74 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ86" s="3" t="inlineStr">
+      <c r="AR86" s="3" t="inlineStr">
         <is>
           <t>your workwear and military surplus range, including Carhartt</t>
         </is>
@@ -16712,26 +17142,31 @@
           <t>None</t>
         </is>
       </c>
-      <c r="AL87" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM87" s="3" t="inlineStr">
+      <c r="AL87" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM87" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN87" s="3" t="inlineStr">
         <is>
           <t>Cold</t>
         </is>
       </c>
-      <c r="AN87" s="3" t="n"/>
-      <c r="AO87" s="4" t="inlineStr">
+      <c r="AO87" s="3" t="n"/>
+      <c r="AP87" s="4" t="inlineStr">
         <is>
           <t>Hi Hannah, I came across your shop and noticed your streetwear edit built around Nike, Adidas and Ralph Lauren. I work with Fleek, a wholesale marketplace connecting retailers and resellers with inventory from trusted suppliers and brands. Would it be useful to see what's currently available that fits what you stock?</t>
         </is>
       </c>
-      <c r="AP87" s="4" t="inlineStr">
+      <c r="AQ87" s="4" t="inlineStr">
         <is>
           <t>Stage identified as New Lead (Cold). Personalisation drawn from notes: your streetwear edit built around Nike, Adidas and Ralph Lauren. No prior contact on record - treated as first outreach.</t>
         </is>
       </c>
-      <c r="AQ87" s="3" t="inlineStr">
+      <c r="AR87" s="3" t="inlineStr">
         <is>
           <t>your streetwear edit built around Nike, Adidas and Ralph Lauren</t>
         </is>
@@ -16901,26 +17336,31 @@
           <t>Missing Contact</t>
         </is>
       </c>
-      <c r="AL88" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM88" s="3" t="inlineStr">
+      <c r="AL88" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM88" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN88" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN88" s="3" t="n"/>
-      <c r="AO88" s="4" t="inlineStr">
+      <c r="AO88" s="3" t="n"/>
+      <c r="AP88" s="4" t="inlineStr">
         <is>
           <t>Hi there, it's been a little while, so wanted to check back in given your 80s/90s denim and sportswear edit. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP88" s="4" t="inlineStr">
+      <c r="AQ88" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Contacted (Re-Engagement). Personalisation drawn from notes: your 80s/90s denim and sportswear edit. Last contacted 91 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ88" s="3" t="inlineStr">
+      <c r="AR88" s="3" t="inlineStr">
         <is>
           <t>your 80s/90s denim and sportswear edit</t>
         </is>
@@ -17090,26 +17530,31 @@
           <t>None</t>
         </is>
       </c>
-      <c r="AL89" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM89" s="3" t="inlineStr">
+      <c r="AL89" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM89" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN89" s="3" t="inlineStr">
         <is>
           <t>Cold</t>
         </is>
       </c>
-      <c r="AN89" s="3" t="n"/>
-      <c r="AO89" s="4" t="inlineStr">
+      <c r="AO89" s="3" t="n"/>
+      <c r="AP89" s="4" t="inlineStr">
         <is>
           <t>Hi Ellie, I came across your shop and noticed your streetwear edit built around Nike, Adidas and Ralph Lauren. I work with Fleek, a wholesale marketplace connecting retailers and resellers with inventory from trusted suppliers and brands. Would it be useful to see what's currently available that fits what you stock?</t>
         </is>
       </c>
-      <c r="AP89" s="4" t="inlineStr">
+      <c r="AQ89" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Contacted (Cold). Personalisation drawn from notes: your streetwear edit built around Nike, Adidas and Ralph Lauren. Last contacted 18 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ89" s="3" t="inlineStr">
+      <c r="AR89" s="3" t="inlineStr">
         <is>
           <t>your streetwear edit built around Nike, Adidas and Ralph Lauren</t>
         </is>
@@ -17279,26 +17724,31 @@
           <t>Missing Website</t>
         </is>
       </c>
-      <c r="AL90" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM90" s="3" t="inlineStr">
+      <c r="AL90" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM90" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN90" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN90" s="3" t="n"/>
-      <c r="AO90" s="4" t="inlineStr">
+      <c r="AO90" s="3" t="n"/>
+      <c r="AP90" s="4" t="inlineStr">
         <is>
           <t>Hi there, it's been a little while, so wanted to check back in given your reworked and archive designer pieces. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP90" s="4" t="inlineStr">
+      <c r="AQ90" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Negotiating (Re-Engagement). Personalisation drawn from notes: your reworked and archive designer pieces. Last contacted 31 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ90" s="3" t="inlineStr">
+      <c r="AR90" s="3" t="inlineStr">
         <is>
           <t>your reworked and archive designer pieces</t>
         </is>
@@ -17468,27 +17918,32 @@
           <t>Non-UK</t>
         </is>
       </c>
-      <c r="AL91" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM91" s="3" t="inlineStr">
+      <c r="AL91" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM91" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN91" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN91" s="3" t="n"/>
-      <c r="AO91" s="4" t="inlineStr">
+      <c r="AO91" s="3" t="n"/>
+      <c r="AP91" s="4" t="inlineStr">
         <is>
           <t>English: Hi Oscar, it's been a little while, so wanted to check back in given your curated womenswear built around Levi's and band tees. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?
 Translated (German): Hallo Oscar, es ist eine Weile her, deshalb wollte ich mich angesichts Ihre kuratierte Damenmode rund um Levi's und Band-T-Shirts noch einmal melden. Kein Druck, falls sich der Zeitpunkt geändert hat, aber falls Beschaffung weiterhin ein Thema für Sie ist, spreche ich gerne wieder darüber. Würde sich ein kurzes Gespräch lohnen?</t>
         </is>
       </c>
-      <c r="AP91" s="4" t="inlineStr">
+      <c r="AQ91" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Quote Sent (Re-Engagement). Personalisation drawn from notes: your curated womenswear built around Levi's and band tees. Last contacted 107 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ91" s="3" t="inlineStr">
+      <c r="AR91" s="3" t="inlineStr">
         <is>
           <t>your curated womenswear built around Levi's and band tees</t>
         </is>
@@ -17658,22 +18113,27 @@
           <t>Non-UK</t>
         </is>
       </c>
-      <c r="AL92" s="3" t="b">
+      <c r="AL92" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM92" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="AM92" s="3" t="inlineStr">
+      <c r="AN92" s="3" t="inlineStr">
         <is>
           <t>No Action</t>
         </is>
       </c>
-      <c r="AN92" s="3" t="n"/>
-      <c r="AO92" s="4" t="inlineStr"/>
-      <c r="AP92" s="4" t="inlineStr">
+      <c r="AO92" s="3" t="n"/>
+      <c r="AP92" s="4" t="inlineStr"/>
+      <c r="AQ92" s="4" t="inlineStr">
         <is>
           <t>Stage 'Not Interested' is on the do-not-message list - no message drafted, no assumptions made about prior conversation content.</t>
         </is>
       </c>
-      <c r="AQ92" s="3" t="inlineStr"/>
+      <c r="AR92" s="3" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
@@ -17839,22 +18299,27 @@
           <t>None</t>
         </is>
       </c>
-      <c r="AL93" s="3" t="b">
+      <c r="AL93" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM93" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="AM93" s="3" t="inlineStr">
+      <c r="AN93" s="3" t="inlineStr">
         <is>
           <t>No Action</t>
         </is>
       </c>
-      <c r="AN93" s="3" t="n"/>
-      <c r="AO93" s="4" t="inlineStr"/>
-      <c r="AP93" s="4" t="inlineStr">
+      <c r="AO93" s="3" t="n"/>
+      <c r="AP93" s="4" t="inlineStr"/>
+      <c r="AQ93" s="4" t="inlineStr">
         <is>
           <t>Stage 'In Conversation' is on the do-not-message list - no message drafted, no assumptions made about prior conversation content.</t>
         </is>
       </c>
-      <c r="AQ93" s="3" t="inlineStr"/>
+      <c r="AR93" s="3" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
@@ -18020,26 +18485,31 @@
           <t>None</t>
         </is>
       </c>
-      <c r="AL94" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM94" s="3" t="inlineStr">
+      <c r="AL94" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM94" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN94" s="3" t="inlineStr">
         <is>
           <t>Customer Check-In</t>
         </is>
       </c>
-      <c r="AN94" s="3" t="n"/>
-      <c r="AO94" s="4" t="inlineStr">
+      <c r="AO94" s="3" t="n"/>
+      <c r="AP94" s="4" t="inlineStr">
         <is>
           <t>Hi Noor, wanted to check in properly rather than send a generic update, given the workwear and military surplus you carry, Carhartt included. Keen to hear how things have been going and whether there's anything new worth exploring together. Not looking to replace that relationship - more to see if we're useful alongside it for specific gaps. Any gaps in what you're sourcing at the moment, or new ranges you're thinking about?</t>
         </is>
       </c>
-      <c r="AP94" s="4" t="inlineStr">
+      <c r="AQ94" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Closed Won (Customer Check-In). Personalisation drawn from notes: your workwear and military surplus range, including Carhartt. Notes flagged a specific objection/context, addressed directly rather than ignored. Last contacted 91 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ94" s="3" t="inlineStr">
+      <c r="AR94" s="3" t="inlineStr">
         <is>
           <t>your workwear and military surplus range, including Carhartt</t>
         </is>
@@ -18209,26 +18679,31 @@
           <t>Possible Duplicate - Unverified</t>
         </is>
       </c>
-      <c r="AL95" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM95" s="5" t="inlineStr">
+      <c r="AL95" s="5" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM95" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN95" s="5" t="inlineStr">
         <is>
           <t>Inbound</t>
         </is>
       </c>
-      <c r="AN95" s="5" t="n"/>
-      <c r="AO95" s="6" t="inlineStr">
+      <c r="AO95" s="5" t="n"/>
+      <c r="AP95" s="6" t="inlineStr">
         <is>
           <t>Hi Mila, thanks for getting in touch - I had a look at your streetwear edit built around Nike, Adidas and Ralph Lauren before writing back. Fleek connects shops like yours with inventory from trusted suppliers, so given the Nike/Adidas/Ralph Lauren streetwear edit you carry, it seemed worth a proper reply rather than a generic one. Since email hasn't been landing, DMs are probably the easier way to reach you. What's the main gap in sourcing right now - more volume, more variety, or something specific you're struggling to find?</t>
         </is>
       </c>
-      <c r="AP95" s="6" t="inlineStr">
+      <c r="AQ95" s="6" t="inlineStr">
         <is>
           <t>Stage identified as Inbound (Inbound). Personalisation drawn from notes: your streetwear edit built around Nike, Adidas and Ralph Lauren. Notes flagged a specific objection/context, addressed directly rather than ignored. No prior contact on record - treated as first outreach.</t>
         </is>
       </c>
-      <c r="AQ95" s="5" t="inlineStr">
+      <c r="AR95" s="5" t="inlineStr">
         <is>
           <t>your streetwear edit built around Nike, Adidas and Ralph Lauren</t>
         </is>
@@ -18398,26 +18873,31 @@
           <t>Missing Contact; Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL96" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM96" s="3" t="inlineStr">
+      <c r="AL96" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM96" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN96" s="3" t="inlineStr">
         <is>
           <t>Churned-Win-Back</t>
         </is>
       </c>
-      <c r="AN96" s="3" t="n"/>
-      <c r="AO96" s="4" t="inlineStr">
+      <c r="AO96" s="3" t="n"/>
+      <c r="AP96" s="4" t="inlineStr">
         <is>
           <t>Hi there, it's been a while since we last worked together, so wanted to reach out honestly rather than pretend nothing's changed. Given your presence across both Depop and Vinted, I understand if the timing wasn't right before. Would it be worth a low-pressure conversation about what's changed on our side, in case it's relevant again?</t>
         </is>
       </c>
-      <c r="AP96" s="4" t="inlineStr">
+      <c r="AQ96" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Lapsed (Churned-Win-Back). Personalisation drawn from notes: selling across both Depop and Vinted. Last contacted 75 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ96" s="3" t="inlineStr">
+      <c r="AR96" s="3" t="inlineStr">
         <is>
           <t>selling across both Depop and Vinted</t>
         </is>
@@ -18587,26 +19067,31 @@
           <t>Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL97" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM97" s="3" t="inlineStr">
+      <c r="AL97" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM97" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN97" s="3" t="inlineStr">
         <is>
           <t>Cold</t>
         </is>
       </c>
-      <c r="AN97" s="3" t="n"/>
-      <c r="AO97" s="4" t="inlineStr">
+      <c r="AO97" s="3" t="n"/>
+      <c r="AP97" s="4" t="inlineStr">
         <is>
           <t>Hi there, I came across your shop and noticed your live-sale format on Whatnot. I work with Fleek, a wholesale marketplace connecting retailers and resellers with inventory from trusted suppliers and brands. Would it be useful to see what's currently available that fits what you stock?</t>
         </is>
       </c>
-      <c r="AP97" s="4" t="inlineStr">
+      <c r="AQ97" s="4" t="inlineStr">
         <is>
           <t>Stage identified as New Lead (Cold). Personalisation drawn from notes: your live-sale format on Whatnot. No prior contact on record - treated as first outreach.</t>
         </is>
       </c>
-      <c r="AQ97" s="3" t="inlineStr">
+      <c r="AR97" s="3" t="inlineStr">
         <is>
           <t>your live-sale format on Whatnot</t>
         </is>
@@ -18776,26 +19261,31 @@
           <t>None</t>
         </is>
       </c>
-      <c r="AL98" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM98" s="3" t="inlineStr">
+      <c r="AL98" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM98" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN98" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN98" s="3" t="n"/>
-      <c r="AO98" s="4" t="inlineStr">
+      <c r="AO98" s="3" t="n"/>
+      <c r="AP98" s="4" t="inlineStr">
         <is>
           <t>Hi there, it's been a little while, so wanted to check back in given your Y2K, grunge and reworked one-off pieces. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP98" s="4" t="inlineStr">
+      <c r="AQ98" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Contacted (Re-Engagement). Personalisation drawn from notes: your Y2K, grunge and reworked one-off pieces. Last contacted 44 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ98" s="3" t="inlineStr">
+      <c r="AR98" s="3" t="inlineStr">
         <is>
           <t>your Y2K, grunge and reworked one-off pieces</t>
         </is>
@@ -18965,26 +19455,31 @@
           <t>Missing Contact; Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL99" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM99" s="3" t="inlineStr">
+      <c r="AL99" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM99" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN99" s="3" t="inlineStr">
         <is>
           <t>Cold</t>
         </is>
       </c>
-      <c r="AN99" s="3" t="n"/>
-      <c r="AO99" s="4" t="inlineStr">
+      <c r="AO99" s="3" t="n"/>
+      <c r="AP99" s="4" t="inlineStr">
         <is>
           <t>Hi there, I came across your shop and noticed running your shop straight through Instagram DMs. I work with Fleek, a wholesale marketplace connecting retailers and resellers with inventory from trusted suppliers and brands. Would it be useful to see what's currently available that fits what you stock?</t>
         </is>
       </c>
-      <c r="AP99" s="4" t="inlineStr">
+      <c r="AQ99" s="4" t="inlineStr">
         <is>
           <t>Stage identified as New Lead (Cold). Personalisation drawn from notes: running your shop straight through Instagram DMs. No prior contact on record - treated as first outreach.</t>
         </is>
       </c>
-      <c r="AQ99" s="3" t="inlineStr">
+      <c r="AR99" s="3" t="inlineStr">
         <is>
           <t>running your shop straight through Instagram DMs</t>
         </is>
@@ -19154,26 +19649,31 @@
           <t>Missing Website</t>
         </is>
       </c>
-      <c r="AL100" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM100" s="3" t="inlineStr">
+      <c r="AL100" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM100" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN100" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN100" s="3" t="n"/>
-      <c r="AO100" s="4" t="inlineStr">
+      <c r="AO100" s="3" t="n"/>
+      <c r="AP100" s="4" t="inlineStr">
         <is>
           <t>Hi Ines, it's been a little while, so wanted to check back in given your curated womenswear built around Levi's and band tees. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Makes sense to see it in action first - I can walk you through the app directly rather than describe it. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP100" s="4" t="inlineStr">
+      <c r="AQ100" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Trial Pending (Re-Engagement). Personalisation drawn from notes: your curated womenswear built around Levi's and band tees. Notes flagged a specific objection/context, addressed directly rather than ignored. Last contacted 128 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ100" s="3" t="inlineStr">
+      <c r="AR100" s="3" t="inlineStr">
         <is>
           <t>your curated womenswear built around Levi's and band tees</t>
         </is>
@@ -19343,26 +19843,31 @@
           <t>Missing Instagram</t>
         </is>
       </c>
-      <c r="AL101" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM101" s="3" t="inlineStr">
+      <c r="AL101" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM101" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN101" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN101" s="3" t="n"/>
-      <c r="AO101" s="4" t="inlineStr">
+      <c r="AO101" s="3" t="n"/>
+      <c r="AP101" s="4" t="inlineStr">
         <is>
           <t>Hi there, it's been a little while, so wanted to check back in given your streetwear edit built around Nike, Adidas and Ralph Lauren. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP101" s="4" t="inlineStr">
+      <c r="AQ101" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Trial Pending (Re-Engagement). Personalisation drawn from notes: your streetwear edit built around Nike, Adidas and Ralph Lauren. Last contacted 73 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ101" s="3" t="inlineStr">
+      <c r="AR101" s="3" t="inlineStr">
         <is>
           <t>your streetwear edit built around Nike, Adidas and Ralph Lauren</t>
         </is>
@@ -19532,26 +20037,31 @@
           <t>Missing Instagram; Possible Duplicate - Unverified</t>
         </is>
       </c>
-      <c r="AL102" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM102" s="5" t="inlineStr">
+      <c r="AL102" s="5" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM102" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN102" s="5" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN102" s="5" t="n"/>
-      <c r="AO102" s="6" t="inlineStr">
+      <c r="AO102" s="5" t="n"/>
+      <c r="AP102" s="6" t="inlineStr">
         <is>
           <t>Hi Chloe, it's been a little while, so wanted to check back in given your retro football shirt and vintage sportswear range. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP102" s="6" t="inlineStr">
+      <c r="AQ102" s="6" t="inlineStr">
         <is>
           <t>Stage identified as Meeting Booked (Re-Engagement). Personalisation drawn from notes: your retro football shirt and vintage sportswear range. Last contacted 25 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ102" s="5" t="inlineStr">
+      <c r="AR102" s="5" t="inlineStr">
         <is>
           <t>your retro football shirt and vintage sportswear range</t>
         </is>
@@ -19721,26 +20231,31 @@
           <t>None</t>
         </is>
       </c>
-      <c r="AL103" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM103" s="3" t="inlineStr">
+      <c r="AL103" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM103" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN103" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN103" s="3" t="n"/>
-      <c r="AO103" s="4" t="inlineStr">
+      <c r="AO103" s="3" t="n"/>
+      <c r="AP103" s="4" t="inlineStr">
         <is>
           <t>Hi there, it's been a little while, so wanted to check back in given your reworked and archive designer pieces. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. No worries on the missed callback - happy to try again whenever suits. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP103" s="4" t="inlineStr">
+      <c r="AQ103" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Contacted (Re-Engagement). Personalisation drawn from notes: your reworked and archive designer pieces. Notes flagged a specific objection/context, addressed directly rather than ignored. Last contacted 96 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ103" s="3" t="inlineStr">
+      <c r="AR103" s="3" t="inlineStr">
         <is>
           <t>your reworked and archive designer pieces</t>
         </is>
@@ -19910,27 +20425,32 @@
           <t>Non-UK</t>
         </is>
       </c>
-      <c r="AL104" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM104" s="3" t="inlineStr">
+      <c r="AL104" s="3" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="AM104" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN104" s="3" t="inlineStr">
         <is>
           <t>Churned-Win-Back</t>
         </is>
       </c>
-      <c r="AN104" s="3" t="n"/>
-      <c r="AO104" s="4" t="inlineStr">
+      <c r="AO104" s="3" t="n"/>
+      <c r="AP104" s="4" t="inlineStr">
         <is>
           <t>English: Hi there, it's been a while since we last worked together, so wanted to reach out honestly rather than pretend nothing's changed. Given the Levi's and band-tee-led womenswear edit you're known for, I understand if the timing wasn't right before. Would it be worth a low-pressure conversation about what's changed on our side, in case it's relevant again?
 Translated (French): Bonjour, cela fait un moment que nous n'avons pas travaillé ensemble, je voulais donc vous recontacter honnêtement plutôt que de faire comme si rien n'avait changé. Étant donné votre sélection femme reconnue autour de Levi's et de t-shirts de groupes de musique, je comprends que le moment n'était peut-être pas idéal auparavant. Cela vaudrait-il la peine d'échanger, sans pression, sur ce qui a changé de notre côté, au cas où cela redeviendrait pertinent ?</t>
         </is>
       </c>
-      <c r="AP104" s="4" t="inlineStr">
+      <c r="AQ104" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Churned (Churned-Win-Back). Personalisation drawn from notes: your curated womenswear built around Levi's and band tees. Last contacted 24 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ104" s="3" t="inlineStr">
+      <c r="AR104" s="3" t="inlineStr">
         <is>
           <t>your curated womenswear built around Levi's and band tees</t>
         </is>
@@ -20100,26 +20620,31 @@
           <t>None</t>
         </is>
       </c>
-      <c r="AL105" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM105" s="3" t="inlineStr">
+      <c r="AL105" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM105" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN105" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN105" s="3" t="n"/>
-      <c r="AO105" s="4" t="inlineStr">
+      <c r="AO105" s="3" t="n"/>
+      <c r="AP105" s="4" t="inlineStr">
         <is>
           <t>Hi Sofia, it's been a little while, so wanted to check back in given your workwear and military surplus range, including Carhartt. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP105" s="4" t="inlineStr">
+      <c r="AQ105" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Quote Sent (Re-Engagement). Personalisation drawn from notes: your workwear and military surplus range, including Carhartt. Last contacted 86 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ105" s="3" t="inlineStr">
+      <c r="AR105" s="3" t="inlineStr">
         <is>
           <t>your workwear and military surplus range, including Carhartt</t>
         </is>
@@ -20289,26 +20814,31 @@
           <t>None</t>
         </is>
       </c>
-      <c r="AL106" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM106" s="3" t="inlineStr">
+      <c r="AL106" s="3" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="AM106" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN106" s="3" t="inlineStr">
         <is>
           <t>Churned-Win-Back</t>
         </is>
       </c>
-      <c r="AN106" s="3" t="n"/>
-      <c r="AO106" s="4" t="inlineStr">
+      <c r="AO106" s="3" t="n"/>
+      <c r="AP106" s="4" t="inlineStr">
         <is>
           <t>Hi there, it's been a while since we last worked together, so wanted to reach out honestly rather than pretend nothing's changed. Given the Levi's and band-tee-led womenswear edit you're known for, I understand if the timing wasn't right before. Would it be worth a low-pressure conversation about what's changed on our side, in case it's relevant again?</t>
         </is>
       </c>
-      <c r="AP106" s="4" t="inlineStr">
+      <c r="AQ106" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Dormant (Churned-Win-Back). Personalisation drawn from notes: your curated womenswear built around Levi's and band tees. Last contacted 20 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ106" s="3" t="inlineStr">
+      <c r="AR106" s="3" t="inlineStr">
         <is>
           <t>your curated womenswear built around Levi's and band tees</t>
         </is>
@@ -20478,26 +21008,31 @@
           <t>Missing Website</t>
         </is>
       </c>
-      <c r="AL107" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM107" s="3" t="inlineStr">
+      <c r="AL107" s="3" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="AM107" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN107" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN107" s="3" t="n"/>
-      <c r="AO107" s="4" t="inlineStr">
+      <c r="AO107" s="3" t="n"/>
+      <c r="AP107" s="4" t="inlineStr">
         <is>
           <t>Hi Marco, it's been a little while, so wanted to check back in given your retro football shirt and vintage sportswear range. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Not looking to replace that relationship - more to see if we're useful alongside it for specific gaps. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP107" s="4" t="inlineStr">
+      <c r="AQ107" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Contacted (Re-Engagement). Personalisation drawn from notes: your retro football shirt and vintage sportswear range. Notes flagged a specific objection/context, addressed directly rather than ignored. Last contacted 84 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ107" s="3" t="inlineStr">
+      <c r="AR107" s="3" t="inlineStr">
         <is>
           <t>your retro football shirt and vintage sportswear range</t>
         </is>
@@ -20667,26 +21202,31 @@
           <t>Missing Contact; Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL108" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM108" s="3" t="inlineStr">
+      <c r="AL108" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM108" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN108" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN108" s="3" t="n"/>
-      <c r="AO108" s="4" t="inlineStr">
+      <c r="AO108" s="3" t="n"/>
+      <c r="AP108" s="4" t="inlineStr">
         <is>
           <t>Hi there, it's been a little while, so wanted to check back in given running your shop straight through Instagram DMs. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP108" s="4" t="inlineStr">
+      <c r="AQ108" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Negotiating (Re-Engagement). Personalisation drawn from notes: running your shop straight through Instagram DMs. Last contacted 21 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ108" s="3" t="inlineStr">
+      <c r="AR108" s="3" t="inlineStr">
         <is>
           <t>running your shop straight through Instagram DMs</t>
         </is>
@@ -20856,26 +21396,31 @@
           <t>Missing Contact; Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL109" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM109" s="3" t="inlineStr">
+      <c r="AL109" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM109" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN109" s="3" t="inlineStr">
         <is>
           <t>Cold</t>
         </is>
       </c>
-      <c r="AN109" s="3" t="n"/>
-      <c r="AO109" s="4" t="inlineStr">
+      <c r="AO109" s="3" t="n"/>
+      <c r="AP109" s="4" t="inlineStr">
         <is>
           <t>Hi there, I came across your shop and noticed your live-sale format on Whatnot. I work with Fleek, a wholesale marketplace connecting retailers and resellers with inventory from trusted suppliers and brands. Would it be useful to see what's currently available that fits what you stock?</t>
         </is>
       </c>
-      <c r="AP109" s="4" t="inlineStr">
+      <c r="AQ109" s="4" t="inlineStr">
         <is>
           <t>Stage identified as New Lead (Cold). Personalisation drawn from notes: your live-sale format on Whatnot. No prior contact on record - treated as first outreach.</t>
         </is>
       </c>
-      <c r="AQ109" s="3" t="inlineStr">
+      <c r="AR109" s="3" t="inlineStr">
         <is>
           <t>your live-sale format on Whatnot</t>
         </is>
@@ -21045,26 +21590,31 @@
           <t>Missing Instagram</t>
         </is>
       </c>
-      <c r="AL110" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM110" s="3" t="inlineStr">
+      <c r="AL110" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM110" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN110" s="3" t="inlineStr">
         <is>
           <t>Cold</t>
         </is>
       </c>
-      <c r="AN110" s="3" t="n"/>
-      <c r="AO110" s="4" t="inlineStr">
+      <c r="AO110" s="3" t="n"/>
+      <c r="AP110" s="4" t="inlineStr">
         <is>
           <t>Hi Grace, I came across your shop and noticed your reworked and archive designer pieces. I work with Fleek, a wholesale marketplace connecting retailers and resellers with inventory from trusted suppliers and brands. Good to put a name to the shop after meeting at the market - still keen to swing by. Would it be useful to see what's currently available that fits what you stock?</t>
         </is>
       </c>
-      <c r="AP110" s="4" t="inlineStr">
+      <c r="AQ110" s="4" t="inlineStr">
         <is>
           <t>Stage identified as New Lead (Cold). Personalisation drawn from notes: your reworked and archive designer pieces. Notes flagged a specific objection/context, addressed directly rather than ignored. No prior contact on record - treated as first outreach.</t>
         </is>
       </c>
-      <c r="AQ110" s="3" t="inlineStr">
+      <c r="AR110" s="3" t="inlineStr">
         <is>
           <t>your reworked and archive designer pieces</t>
         </is>
@@ -21234,26 +21784,31 @@
           <t>Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL111" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM111" s="3" t="inlineStr">
+      <c r="AL111" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM111" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN111" s="3" t="inlineStr">
         <is>
           <t>Customer Check-In</t>
         </is>
       </c>
-      <c r="AN111" s="3" t="n"/>
-      <c r="AO111" s="4" t="inlineStr">
+      <c r="AO111" s="3" t="n"/>
+      <c r="AP111" s="4" t="inlineStr">
         <is>
           <t>Hi there, wanted to check in properly rather than send a generic update, given the DM-led way you run sales. Keen to hear how things have been going and whether there's anything new worth exploring together. Any gaps in what you're sourcing at the moment, or new ranges you're thinking about?</t>
         </is>
       </c>
-      <c r="AP111" s="4" t="inlineStr">
+      <c r="AQ111" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Closed Won (Customer Check-In). Personalisation drawn from notes: running your shop straight through Instagram DMs. Last contacted 85 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ111" s="3" t="inlineStr">
+      <c r="AR111" s="3" t="inlineStr">
         <is>
           <t>running your shop straight through Instagram DMs</t>
         </is>
@@ -21423,26 +21978,31 @@
           <t>Non-UK</t>
         </is>
       </c>
-      <c r="AL112" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM112" s="3" t="inlineStr">
+      <c r="AL112" s="3" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="AM112" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN112" s="3" t="inlineStr">
         <is>
           <t>Inbound</t>
         </is>
       </c>
-      <c r="AN112" s="3" t="n"/>
-      <c r="AO112" s="4" t="inlineStr">
+      <c r="AO112" s="3" t="n"/>
+      <c r="AP112" s="4" t="inlineStr">
         <is>
           <t>Hi Karim, thanks for getting in touch - I had a look at your hand-picked edit spanning the 60s through the 90s before writing back. Fleek connects shops like yours with inventory from trusted suppliers, so given the decades-spanning edit you've hand-picked, it seemed worth a proper reply rather than a generic one. What's the main gap in sourcing right now - more volume, more variety, or something specific you're struggling to find?</t>
         </is>
       </c>
-      <c r="AP112" s="4" t="inlineStr">
+      <c r="AQ112" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Inbound (Inbound). Personalisation drawn from notes: your hand-picked edit spanning the 60s through the 90s. No prior contact on record - treated as first outreach.</t>
         </is>
       </c>
-      <c r="AQ112" s="3" t="inlineStr">
+      <c r="AR112" s="3" t="inlineStr">
         <is>
           <t>your hand-picked edit spanning the 60s through the 90s</t>
         </is>
@@ -21612,26 +22172,31 @@
           <t>Missing Contact; Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL113" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM113" s="3" t="inlineStr">
+      <c r="AL113" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM113" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN113" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN113" s="3" t="n"/>
-      <c r="AO113" s="4" t="inlineStr">
+      <c r="AO113" s="3" t="n"/>
+      <c r="AP113" s="4" t="inlineStr">
         <is>
           <t>Hi there, it's been a little while, so wanted to check back in given selling through Depop. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP113" s="4" t="inlineStr">
+      <c r="AQ113" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Trial Pending (Re-Engagement). Personalisation drawn from channel (notes unavailable): selling through Depop. Last contacted 27 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ113" s="3" t="inlineStr">
+      <c r="AR113" s="3" t="inlineStr">
         <is>
           <t>selling through Depop</t>
         </is>
@@ -21801,26 +22366,31 @@
           <t>Missing Contact; Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL114" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM114" s="3" t="inlineStr">
+      <c r="AL114" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM114" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN114" s="3" t="inlineStr">
         <is>
           <t>Cold</t>
         </is>
       </c>
-      <c r="AN114" s="3" t="n"/>
-      <c r="AO114" s="4" t="inlineStr">
+      <c r="AO114" s="3" t="n"/>
+      <c r="AP114" s="4" t="inlineStr">
         <is>
           <t>Hi there, I came across your shop and noticed your live-sale format on Whatnot. I work with Fleek, a wholesale marketplace connecting retailers and resellers with inventory from trusted suppliers and brands. Would it be useful to see what's currently available that fits what you stock?</t>
         </is>
       </c>
-      <c r="AP114" s="4" t="inlineStr">
+      <c r="AQ114" s="4" t="inlineStr">
         <is>
           <t>Stage identified as New Lead (Cold). Personalisation drawn from notes: your live-sale format on Whatnot. No prior contact on record - treated as first outreach.</t>
         </is>
       </c>
-      <c r="AQ114" s="3" t="inlineStr">
+      <c r="AR114" s="3" t="inlineStr">
         <is>
           <t>your live-sale format on Whatnot</t>
         </is>
@@ -21990,27 +22560,32 @@
           <t>Non-UK</t>
         </is>
       </c>
-      <c r="AL115" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM115" s="3" t="inlineStr">
+      <c r="AL115" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM115" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN115" s="3" t="inlineStr">
         <is>
           <t>Cold</t>
         </is>
       </c>
-      <c r="AN115" s="3" t="n"/>
-      <c r="AO115" s="4" t="inlineStr">
+      <c r="AO115" s="3" t="n"/>
+      <c r="AP115" s="4" t="inlineStr">
         <is>
           <t>English: Hi Theo, I came across your shop and noticed your hand-picked edit spanning the 60s through the 90s. I work with Fleek, a wholesale marketplace connecting retailers and resellers with inventory from trusted suppliers and brands. Makes sense to see it in action first - I can walk you through the app directly rather than describe it. Would it be useful to see what's currently available that fits what you stock?
 Translated (German): Hallo Theo, ich bin auf Ihr Geschäft gestoßen und habe Ihre handverlesene Auswahl von den 60ern bis zu den 90ern bemerkt. Ich arbeite mit Fleek, einem Großhandelsmarktplatz, der Einzelhändler und Wiederverkäufer mit vertrauenswürdigen Lieferanten und Marken verbindet. Die App vorher zu sehen, ist absolut nachvollziehbar - ich zeige sie Ihnen gerne direkt, statt sie nur zu beschreiben. Wäre es interessant zu sehen, was aktuell verfügbar ist und zu Ihrem Sortiment passt?</t>
         </is>
       </c>
-      <c r="AP115" s="4" t="inlineStr">
+      <c r="AQ115" s="4" t="inlineStr">
         <is>
           <t>Stage identified as New Lead (Cold). Personalisation drawn from notes: your hand-picked edit spanning the 60s through the 90s. Notes flagged a specific objection/context, addressed directly rather than ignored. No prior contact on record - treated as first outreach.</t>
         </is>
       </c>
-      <c r="AQ115" s="3" t="inlineStr">
+      <c r="AR115" s="3" t="inlineStr">
         <is>
           <t>your hand-picked edit spanning the 60s through the 90s</t>
         </is>
@@ -22180,22 +22755,27 @@
           <t>Non-UK</t>
         </is>
       </c>
-      <c r="AL116" s="3" t="b">
+      <c r="AL116" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM116" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="AM116" s="3" t="inlineStr">
+      <c r="AN116" s="3" t="inlineStr">
         <is>
           <t>No Action</t>
         </is>
       </c>
-      <c r="AN116" s="3" t="n"/>
-      <c r="AO116" s="4" t="inlineStr"/>
-      <c r="AP116" s="4" t="inlineStr">
+      <c r="AO116" s="3" t="n"/>
+      <c r="AP116" s="4" t="inlineStr"/>
+      <c r="AQ116" s="4" t="inlineStr">
         <is>
           <t>Stage 'In Conversation' is on the do-not-message list - no message drafted, no assumptions made about prior conversation content.</t>
         </is>
       </c>
-      <c r="AQ116" s="3" t="inlineStr"/>
+      <c r="AR116" s="3" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
@@ -22361,26 +22941,31 @@
           <t>None</t>
         </is>
       </c>
-      <c r="AL117" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM117" s="3" t="inlineStr">
+      <c r="AL117" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM117" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN117" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN117" s="3" t="n"/>
-      <c r="AO117" s="4" t="inlineStr">
+      <c r="AO117" s="3" t="n"/>
+      <c r="AP117" s="4" t="inlineStr">
         <is>
           <t>Hi Tom, it's been a little while, so wanted to check back in given your streetwear edit built around Nike, Adidas and Ralph Lauren. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick correction on that: we work with shops at a range of sizes, not just small resellers - happy to show you what that actually looks like. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP117" s="4" t="inlineStr">
+      <c r="AQ117" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Negotiating (Re-Engagement). Personalisation drawn from notes: your streetwear edit built around Nike, Adidas and Ralph Lauren. Notes flagged a specific objection/context, addressed directly rather than ignored. Last contacted 24 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ117" s="3" t="inlineStr">
+      <c r="AR117" s="3" t="inlineStr">
         <is>
           <t>your streetwear edit built around Nike, Adidas and Ralph Lauren</t>
         </is>
@@ -22550,22 +23135,27 @@
           <t>None</t>
         </is>
       </c>
-      <c r="AL118" s="3" t="b">
+      <c r="AL118" s="3" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="AM118" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="AM118" s="3" t="inlineStr">
+      <c r="AN118" s="3" t="inlineStr">
         <is>
           <t>No Action</t>
         </is>
       </c>
-      <c r="AN118" s="3" t="n"/>
-      <c r="AO118" s="4" t="inlineStr"/>
-      <c r="AP118" s="4" t="inlineStr">
+      <c r="AO118" s="3" t="n"/>
+      <c r="AP118" s="4" t="inlineStr"/>
+      <c r="AQ118" s="4" t="inlineStr">
         <is>
           <t>Stage 'Closed Lost' is on the do-not-message list - no message drafted, no assumptions made about prior conversation content.</t>
         </is>
       </c>
-      <c r="AQ118" s="3" t="inlineStr"/>
+      <c r="AR118" s="3" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
@@ -22731,26 +23321,31 @@
           <t>Missing Contact; Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL119" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM119" s="3" t="inlineStr">
+      <c r="AL119" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM119" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN119" s="3" t="inlineStr">
         <is>
           <t>Churned-Win-Back</t>
         </is>
       </c>
-      <c r="AN119" s="3" t="n"/>
-      <c r="AO119" s="4" t="inlineStr">
+      <c r="AO119" s="3" t="n"/>
+      <c r="AP119" s="4" t="inlineStr">
         <is>
           <t>Hi there, it's been a while since we last worked together, so wanted to reach out honestly rather than pretend nothing's changed. Given the fast sell-through you've been getting, I understand if the timing wasn't right before. Would it be worth a low-pressure conversation about what's changed on our side, in case it's relevant again?</t>
         </is>
       </c>
-      <c r="AP119" s="4" t="inlineStr">
+      <c r="AQ119" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Churned (Churned-Win-Back). Personalisation drawn from notes: how quickly your stock turns over. Last contacted 71 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ119" s="3" t="inlineStr">
+      <c r="AR119" s="3" t="inlineStr">
         <is>
           <t>how quickly your stock turns over</t>
         </is>
@@ -22920,26 +23515,31 @@
           <t>Missing Contact; Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL120" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM120" s="3" t="inlineStr">
+      <c r="AL120" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM120" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN120" s="3" t="inlineStr">
         <is>
           <t>Inbound</t>
         </is>
       </c>
-      <c r="AN120" s="3" t="n"/>
-      <c r="AO120" s="4" t="inlineStr">
+      <c r="AO120" s="3" t="n"/>
+      <c r="AP120" s="4" t="inlineStr">
         <is>
           <t>Hi there, thanks for getting in touch - I had a look at selling through Depop before writing back. Fleek connects shops like yours with inventory from trusted suppliers, so given your Depop shop, it seemed worth a proper reply rather than a generic one. What's the main gap in sourcing right now - more volume, more variety, or something specific you're struggling to find?</t>
         </is>
       </c>
-      <c r="AP120" s="4" t="inlineStr">
+      <c r="AQ120" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Inbound (Inbound). Personalisation drawn from channel (notes unavailable): selling through Depop. No prior contact on record - treated as first outreach.</t>
         </is>
       </c>
-      <c r="AQ120" s="3" t="inlineStr">
+      <c r="AR120" s="3" t="inlineStr">
         <is>
           <t>selling through Depop</t>
         </is>
@@ -23109,26 +23709,31 @@
           <t>Missing Contact; Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL121" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM121" s="3" t="inlineStr">
+      <c r="AL121" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM121" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN121" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN121" s="3" t="n"/>
-      <c r="AO121" s="4" t="inlineStr">
+      <c r="AO121" s="3" t="n"/>
+      <c r="AP121" s="4" t="inlineStr">
         <is>
           <t>Hi there, it's been a little while, so wanted to check back in given how quickly your stock turns over. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP121" s="4" t="inlineStr">
+      <c r="AQ121" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Contacted (Re-Engagement). Personalisation drawn from notes: how quickly your stock turns over. Last contacted 101 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ121" s="3" t="inlineStr">
+      <c r="AR121" s="3" t="inlineStr">
         <is>
           <t>how quickly your stock turns over</t>
         </is>
@@ -23298,26 +23903,31 @@
           <t>Missing Contact; Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL122" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM122" s="3" t="inlineStr">
+      <c r="AL122" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM122" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN122" s="3" t="inlineStr">
         <is>
           <t>Cold</t>
         </is>
       </c>
-      <c r="AN122" s="3" t="n"/>
-      <c r="AO122" s="4" t="inlineStr">
+      <c r="AO122" s="3" t="n"/>
+      <c r="AP122" s="4" t="inlineStr">
         <is>
           <t>Hi there, I came across your shop and noticed running sales through Instagram. I work with Fleek, a wholesale marketplace connecting retailers and resellers with inventory from trusted suppliers and brands. Would it be useful to see what's currently available that fits what you stock?</t>
         </is>
       </c>
-      <c r="AP122" s="4" t="inlineStr">
+      <c r="AQ122" s="4" t="inlineStr">
         <is>
           <t>Stage identified as New Lead (Cold). Personalisation drawn from channel (notes unavailable): running sales through Instagram. No prior contact on record - treated as first outreach.</t>
         </is>
       </c>
-      <c r="AQ122" s="3" t="inlineStr">
+      <c r="AR122" s="3" t="inlineStr">
         <is>
           <t>running sales through Instagram</t>
         </is>
@@ -23487,26 +24097,31 @@
           <t>Missing Contact; Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL123" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM123" s="3" t="inlineStr">
+      <c r="AL123" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM123" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN123" s="3" t="inlineStr">
         <is>
           <t>Churned-Win-Back</t>
         </is>
       </c>
-      <c r="AN123" s="3" t="n"/>
-      <c r="AO123" s="4" t="inlineStr">
+      <c r="AO123" s="3" t="n"/>
+      <c r="AP123" s="4" t="inlineStr">
         <is>
           <t>Hi there, it's been a while since we last worked together, so wanted to reach out honestly rather than pretend nothing's changed. Given your Vinted shop, I understand if the timing wasn't right before. Would it be worth a low-pressure conversation about what's changed on our side, in case it's relevant again?</t>
         </is>
       </c>
-      <c r="AP123" s="4" t="inlineStr">
+      <c r="AQ123" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Churned (Churned-Win-Back). Personalisation drawn from channel (notes unavailable): selling through Vinted. Last contacted 76 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ123" s="3" t="inlineStr">
+      <c r="AR123" s="3" t="inlineStr">
         <is>
           <t>selling through Vinted</t>
         </is>
@@ -23676,26 +24291,31 @@
           <t>None</t>
         </is>
       </c>
-      <c r="AL124" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM124" s="3" t="inlineStr">
+      <c r="AL124" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM124" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN124" s="3" t="inlineStr">
         <is>
           <t>Churned-Win-Back</t>
         </is>
       </c>
-      <c r="AN124" s="3" t="n"/>
-      <c r="AO124" s="4" t="inlineStr">
+      <c r="AO124" s="3" t="n"/>
+      <c r="AP124" s="4" t="inlineStr">
         <is>
           <t>Hi there, it's been a while since we last worked together, so wanted to reach out honestly rather than pretend nothing's changed. Given the Y2K and grunge one-offs you carry, I understand if the timing wasn't right before. Since email hasn't been landing, DMs are probably the easier way to reach you. Would it be worth a low-pressure conversation about what's changed on our side, in case it's relevant again?</t>
         </is>
       </c>
-      <c r="AP124" s="4" t="inlineStr">
+      <c r="AQ124" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Stopped Buying (Churned-Win-Back). Personalisation drawn from notes: your Y2K, grunge and reworked one-off pieces. Notes flagged a specific objection/context, addressed directly rather than ignored. Last contacted 55 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ124" s="3" t="inlineStr">
+      <c r="AR124" s="3" t="inlineStr">
         <is>
           <t>your Y2K, grunge and reworked one-off pieces</t>
         </is>
@@ -23865,26 +24485,31 @@
           <t>None</t>
         </is>
       </c>
-      <c r="AL125" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM125" s="3" t="inlineStr">
+      <c r="AL125" s="3" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="AM125" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN125" s="3" t="inlineStr">
         <is>
           <t>Cold</t>
         </is>
       </c>
-      <c r="AN125" s="3" t="n"/>
-      <c r="AO125" s="4" t="inlineStr">
+      <c r="AO125" s="3" t="n"/>
+      <c r="AP125" s="4" t="inlineStr">
         <is>
           <t>Hi Noor, I came across your shop and noticed your curated womenswear built around Levi's and band tees. I work with Fleek, a wholesale marketplace connecting retailers and resellers with inventory from trusted suppliers and brands. Not looking to replace that relationship - more to see if we're useful alongside it for specific gaps. Would it be useful to see what's currently available that fits what you stock?</t>
         </is>
       </c>
-      <c r="AP125" s="4" t="inlineStr">
+      <c r="AQ125" s="4" t="inlineStr">
         <is>
           <t>Stage identified as New Lead (Cold). Personalisation drawn from notes: your curated womenswear built around Levi's and band tees. Notes flagged a specific objection/context, addressed directly rather than ignored. No prior contact on record - treated as first outreach.</t>
         </is>
       </c>
-      <c r="AQ125" s="3" t="inlineStr">
+      <c r="AR125" s="3" t="inlineStr">
         <is>
           <t>your curated womenswear built around Levi's and band tees</t>
         </is>
@@ -24054,22 +24679,27 @@
           <t>None</t>
         </is>
       </c>
-      <c r="AL126" s="3" t="b">
+      <c r="AL126" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM126" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="AM126" s="3" t="inlineStr">
+      <c r="AN126" s="3" t="inlineStr">
         <is>
           <t>No Action</t>
         </is>
       </c>
-      <c r="AN126" s="3" t="n"/>
-      <c r="AO126" s="4" t="inlineStr"/>
-      <c r="AP126" s="4" t="inlineStr">
+      <c r="AO126" s="3" t="n"/>
+      <c r="AP126" s="4" t="inlineStr"/>
+      <c r="AQ126" s="4" t="inlineStr">
         <is>
           <t>Stage 'In Conversation' is on the do-not-message list - no message drafted, no assumptions made about prior conversation content.</t>
         </is>
       </c>
-      <c r="AQ126" s="3" t="inlineStr"/>
+      <c r="AR126" s="3" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
@@ -24235,26 +24865,31 @@
           <t>Missing Website</t>
         </is>
       </c>
-      <c r="AL127" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM127" s="3" t="inlineStr">
+      <c r="AL127" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM127" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN127" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN127" s="3" t="n"/>
-      <c r="AO127" s="4" t="inlineStr">
+      <c r="AO127" s="3" t="n"/>
+      <c r="AP127" s="4" t="inlineStr">
         <is>
           <t>Hi there, it's been a little while, so wanted to check back in given your Y2K, grunge and reworked one-off pieces. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Good to put a name to the shop after meeting at the market - still keen to swing by. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP127" s="4" t="inlineStr">
+      <c r="AQ127" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Contacted (Re-Engagement). Personalisation drawn from notes: your Y2K, grunge and reworked one-off pieces. Notes flagged a specific objection/context, addressed directly rather than ignored. Last contacted 50 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ127" s="3" t="inlineStr">
+      <c r="AR127" s="3" t="inlineStr">
         <is>
           <t>your Y2K, grunge and reworked one-off pieces</t>
         </is>
@@ -24424,22 +25059,27 @@
           <t>Missing Contact; Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL128" s="3" t="b">
+      <c r="AL128" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM128" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="AM128" s="3" t="inlineStr">
+      <c r="AN128" s="3" t="inlineStr">
         <is>
           <t>No Action</t>
         </is>
       </c>
-      <c r="AN128" s="3" t="n"/>
-      <c r="AO128" s="4" t="inlineStr"/>
-      <c r="AP128" s="4" t="inlineStr">
+      <c r="AO128" s="3" t="n"/>
+      <c r="AP128" s="4" t="inlineStr"/>
+      <c r="AQ128" s="4" t="inlineStr">
         <is>
           <t>Stage 'Closed Lost' is on the do-not-message list - no message drafted, no assumptions made about prior conversation content.</t>
         </is>
       </c>
-      <c r="AQ128" s="3" t="inlineStr"/>
+      <c r="AR128" s="3" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
@@ -24605,26 +25245,31 @@
           <t>Missing Website; Possible Duplicate - Unverified</t>
         </is>
       </c>
-      <c r="AL129" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM129" s="5" t="inlineStr">
+      <c r="AL129" s="5" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM129" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN129" s="5" t="inlineStr">
         <is>
           <t>Cold</t>
         </is>
       </c>
-      <c r="AN129" s="5" t="n"/>
-      <c r="AO129" s="6" t="inlineStr">
+      <c r="AO129" s="5" t="n"/>
+      <c r="AP129" s="6" t="inlineStr">
         <is>
           <t>Hi there, I came across your shop and noticed your hand-picked edit spanning the 60s through the 90s. I work with Fleek, a wholesale marketplace connecting retailers and resellers with inventory from trusted suppliers and brands. Good to put a name to the shop after meeting at the market - still keen to swing by. Would it be useful to see what's currently available that fits what you stock?</t>
         </is>
       </c>
-      <c r="AP129" s="6" t="inlineStr">
+      <c r="AQ129" s="6" t="inlineStr">
         <is>
           <t>Stage identified as New Lead (Cold). Personalisation drawn from notes: your hand-picked edit spanning the 60s through the 90s. Notes flagged a specific objection/context, addressed directly rather than ignored. No prior contact on record - treated as first outreach.</t>
         </is>
       </c>
-      <c r="AQ129" s="5" t="inlineStr">
+      <c r="AR129" s="5" t="inlineStr">
         <is>
           <t>your hand-picked edit spanning the 60s through the 90s</t>
         </is>
@@ -24794,26 +25439,31 @@
           <t>Missing Website; Possible Duplicate - Unverified</t>
         </is>
       </c>
-      <c r="AL130" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM130" s="5" t="inlineStr">
+      <c r="AL130" s="5" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM130" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN130" s="5" t="inlineStr">
         <is>
           <t>Churned-Win-Back</t>
         </is>
       </c>
-      <c r="AN130" s="5" t="n"/>
-      <c r="AO130" s="6" t="inlineStr">
+      <c r="AO130" s="5" t="n"/>
+      <c r="AP130" s="6" t="inlineStr">
         <is>
           <t>Hi there, it's been a while since we last worked together, so wanted to reach out honestly rather than pretend nothing's changed. Given the Levi's and band-tee-led womenswear edit you're known for, I understand if the timing wasn't right before. Fair to compare - happy to let the numbers speak for themselves rather than argue the case. Would it be worth a low-pressure conversation about what's changed on our side, in case it's relevant again?</t>
         </is>
       </c>
-      <c r="AP130" s="6" t="inlineStr">
+      <c r="AQ130" s="6" t="inlineStr">
         <is>
           <t>Stage identified as Stopped Buying (Churned-Win-Back). Personalisation drawn from notes: your curated womenswear built around Levi's and band tees. Notes flagged a specific objection/context, addressed directly rather than ignored. Last contacted 107 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ130" s="5" t="inlineStr">
+      <c r="AR130" s="5" t="inlineStr">
         <is>
           <t>your curated womenswear built around Levi's and band tees</t>
         </is>
@@ -24983,26 +25633,31 @@
           <t>None</t>
         </is>
       </c>
-      <c r="AL131" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM131" s="3" t="inlineStr">
+      <c r="AL131" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM131" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN131" s="3" t="inlineStr">
         <is>
           <t>Inbound</t>
         </is>
       </c>
-      <c r="AN131" s="3" t="n"/>
-      <c r="AO131" s="4" t="inlineStr">
+      <c r="AO131" s="3" t="n"/>
+      <c r="AP131" s="4" t="inlineStr">
         <is>
           <t>Hi Freya, thanks for getting in touch - I had a look at your curated womenswear built around Levi's and band tees before writing back. Fleek connects shops like yours with inventory from trusted suppliers, so given the Levi's and band-tee-led womenswear edit you're known for, it seemed worth a proper reply rather than a generic one. What's the main gap in sourcing right now - more volume, more variety, or something specific you're struggling to find?</t>
         </is>
       </c>
-      <c r="AP131" s="4" t="inlineStr">
+      <c r="AQ131" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Inbound (Inbound). Personalisation drawn from notes: your curated womenswear built around Levi's and band tees. No prior contact on record - treated as first outreach.</t>
         </is>
       </c>
-      <c r="AQ131" s="3" t="inlineStr">
+      <c r="AR131" s="3" t="inlineStr">
         <is>
           <t>your curated womenswear built around Levi's and band tees</t>
         </is>
@@ -25172,26 +25827,31 @@
           <t>Missing Contact; Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL132" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM132" s="3" t="inlineStr">
+      <c r="AL132" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM132" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN132" s="3" t="inlineStr">
         <is>
           <t>Churned-Win-Back</t>
         </is>
       </c>
-      <c r="AN132" s="3" t="n"/>
-      <c r="AO132" s="4" t="inlineStr">
+      <c r="AO132" s="3" t="n"/>
+      <c r="AP132" s="4" t="inlineStr">
         <is>
           <t>Hi there, it's been a while since we last worked together, so wanted to reach out honestly rather than pretend nothing's changed. Given the fast sell-through you've been getting, I understand if the timing wasn't right before. Would it be worth a low-pressure conversation about what's changed on our side, in case it's relevant again?</t>
         </is>
       </c>
-      <c r="AP132" s="4" t="inlineStr">
+      <c r="AQ132" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Churned (Churned-Win-Back). Personalisation drawn from notes: how quickly your stock turns over. Last contacted 41 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ132" s="3" t="inlineStr">
+      <c r="AR132" s="3" t="inlineStr">
         <is>
           <t>how quickly your stock turns over</t>
         </is>
@@ -25361,26 +26021,31 @@
           <t>Missing Website</t>
         </is>
       </c>
-      <c r="AL133" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM133" s="3" t="inlineStr">
+      <c r="AL133" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM133" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN133" s="3" t="inlineStr">
         <is>
           <t>Cold</t>
         </is>
       </c>
-      <c r="AN133" s="3" t="n"/>
-      <c r="AO133" s="4" t="inlineStr">
+      <c r="AO133" s="3" t="n"/>
+      <c r="AP133" s="4" t="inlineStr">
         <is>
           <t>Hi Oscar, I came across your shop and noticed your Y2K, grunge and reworked one-off pieces. I work with Fleek, a wholesale marketplace connecting retailers and resellers with inventory from trusted suppliers and brands. Would it be useful to see what's currently available that fits what you stock?</t>
         </is>
       </c>
-      <c r="AP133" s="4" t="inlineStr">
+      <c r="AQ133" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Contacted (Cold). Personalisation drawn from notes: your Y2K, grunge and reworked one-off pieces. Last contacted 24 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ133" s="3" t="inlineStr">
+      <c r="AR133" s="3" t="inlineStr">
         <is>
           <t>your Y2K, grunge and reworked one-off pieces</t>
         </is>
@@ -25550,26 +26215,31 @@
           <t>Missing Contact; Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL134" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM134" s="3" t="inlineStr">
+      <c r="AL134" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM134" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN134" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN134" s="3" t="n"/>
-      <c r="AO134" s="4" t="inlineStr">
+      <c r="AO134" s="3" t="n"/>
+      <c r="AP134" s="4" t="inlineStr">
         <is>
           <t>Hi there, it's been a little while, so wanted to check back in given selling across both Depop and Vinted. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP134" s="4" t="inlineStr">
+      <c r="AQ134" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Contacted (Re-Engagement). Personalisation drawn from notes: selling across both Depop and Vinted. Last contacted 69 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ134" s="3" t="inlineStr">
+      <c r="AR134" s="3" t="inlineStr">
         <is>
           <t>selling across both Depop and Vinted</t>
         </is>
@@ -25739,26 +26409,31 @@
           <t>Missing Contact; Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL135" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM135" s="3" t="inlineStr">
+      <c r="AL135" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM135" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN135" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN135" s="3" t="n"/>
-      <c r="AO135" s="4" t="inlineStr">
+      <c r="AO135" s="3" t="n"/>
+      <c r="AP135" s="4" t="inlineStr">
         <is>
           <t>Hi there, it's been a little while, so wanted to check back in given running sales through Instagram. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP135" s="4" t="inlineStr">
+      <c r="AQ135" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Negotiating (Re-Engagement). Personalisation drawn from channel (notes unavailable): running sales through Instagram. Last contacted 15 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ135" s="3" t="inlineStr">
+      <c r="AR135" s="3" t="inlineStr">
         <is>
           <t>running sales through Instagram</t>
         </is>
@@ -25928,26 +26603,31 @@
           <t>None</t>
         </is>
       </c>
-      <c r="AL136" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM136" s="3" t="inlineStr">
+      <c r="AL136" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM136" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN136" s="3" t="inlineStr">
         <is>
           <t>Cold</t>
         </is>
       </c>
-      <c r="AN136" s="3" t="n"/>
-      <c r="AO136" s="4" t="inlineStr">
+      <c r="AO136" s="3" t="n"/>
+      <c r="AP136" s="4" t="inlineStr">
         <is>
           <t>Hi there, I came across your shop and noticed your streetwear edit built around Nike, Adidas and Ralph Lauren. I work with Fleek, a wholesale marketplace connecting retailers and resellers with inventory from trusted suppliers and brands. No worries on the missed callback - happy to try again whenever suits. Would it be useful to see what's currently available that fits what you stock?</t>
         </is>
       </c>
-      <c r="AP136" s="4" t="inlineStr">
+      <c r="AQ136" s="4" t="inlineStr">
         <is>
           <t>Stage identified as New Lead (Cold). Personalisation drawn from notes: your streetwear edit built around Nike, Adidas and Ralph Lauren. Notes flagged a specific objection/context, addressed directly rather than ignored. No prior contact on record - treated as first outreach.</t>
         </is>
       </c>
-      <c r="AQ136" s="3" t="inlineStr">
+      <c r="AR136" s="3" t="inlineStr">
         <is>
           <t>your streetwear edit built around Nike, Adidas and Ralph Lauren</t>
         </is>
@@ -26117,26 +26797,31 @@
           <t>Missing Contact; Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL137" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM137" s="3" t="inlineStr">
+      <c r="AL137" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM137" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN137" s="3" t="inlineStr">
         <is>
           <t>Cold</t>
         </is>
       </c>
-      <c r="AN137" s="3" t="n"/>
-      <c r="AO137" s="4" t="inlineStr">
+      <c r="AO137" s="3" t="n"/>
+      <c r="AP137" s="4" t="inlineStr">
         <is>
           <t>Hi there, I came across your shop and noticed selling through Depop. I work with Fleek, a wholesale marketplace connecting retailers and resellers with inventory from trusted suppliers and brands. Would it be useful to see what's currently available that fits what you stock?</t>
         </is>
       </c>
-      <c r="AP137" s="4" t="inlineStr">
+      <c r="AQ137" s="4" t="inlineStr">
         <is>
           <t>Stage identified as New Lead (Cold). Personalisation drawn from channel (notes unavailable): selling through Depop. No prior contact on record - treated as first outreach.</t>
         </is>
       </c>
-      <c r="AQ137" s="3" t="inlineStr">
+      <c r="AR137" s="3" t="inlineStr">
         <is>
           <t>selling through Depop</t>
         </is>
@@ -26306,26 +26991,31 @@
           <t>Missing Contact; Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL138" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM138" s="3" t="inlineStr">
+      <c r="AL138" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM138" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN138" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN138" s="3" t="n"/>
-      <c r="AO138" s="4" t="inlineStr">
+      <c r="AO138" s="3" t="n"/>
+      <c r="AP138" s="4" t="inlineStr">
         <is>
           <t>Hi there, it's been a little while, so wanted to check back in given how quickly your stock turns over. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP138" s="4" t="inlineStr">
+      <c r="AQ138" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Replied (Re-Engagement). Personalisation drawn from notes: how quickly your stock turns over. Last contacted 88 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ138" s="3" t="inlineStr">
+      <c r="AR138" s="3" t="inlineStr">
         <is>
           <t>how quickly your stock turns over</t>
         </is>
@@ -26495,26 +27185,31 @@
           <t>None</t>
         </is>
       </c>
-      <c r="AL139" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM139" s="3" t="inlineStr">
+      <c r="AL139" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM139" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN139" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN139" s="3" t="n"/>
-      <c r="AO139" s="4" t="inlineStr">
+      <c r="AO139" s="3" t="n"/>
+      <c r="AP139" s="4" t="inlineStr">
         <is>
           <t>Hi there, it's been a little while, so wanted to check back in given your workwear and military surplus range, including Carhartt. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Fair to compare - happy to let the numbers speak for themselves rather than argue the case. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP139" s="4" t="inlineStr">
+      <c r="AQ139" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Replied (Re-Engagement). Personalisation drawn from notes: your workwear and military surplus range, including Carhartt. Notes flagged a specific objection/context, addressed directly rather than ignored. Last contacted 125 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ139" s="3" t="inlineStr">
+      <c r="AR139" s="3" t="inlineStr">
         <is>
           <t>your workwear and military surplus range, including Carhartt</t>
         </is>
@@ -26684,26 +27379,31 @@
           <t>Missing Website</t>
         </is>
       </c>
-      <c r="AL140" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM140" s="3" t="inlineStr">
+      <c r="AL140" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM140" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN140" s="3" t="inlineStr">
         <is>
           <t>Cold</t>
         </is>
       </c>
-      <c r="AN140" s="3" t="n"/>
-      <c r="AO140" s="4" t="inlineStr">
+      <c r="AO140" s="3" t="n"/>
+      <c r="AP140" s="4" t="inlineStr">
         <is>
           <t>Hi Priya, I came across your shop and noticed your workwear and military surplus range, including Carhartt. I work with Fleek, a wholesale marketplace connecting retailers and resellers with inventory from trusted suppliers and brands. Would it be useful to see what's currently available that fits what you stock?</t>
         </is>
       </c>
-      <c r="AP140" s="4" t="inlineStr">
+      <c r="AQ140" s="4" t="inlineStr">
         <is>
           <t>Stage identified as New Lead (Cold). Personalisation drawn from notes: your workwear and military surplus range, including Carhartt. No prior contact on record - treated as first outreach.</t>
         </is>
       </c>
-      <c r="AQ140" s="3" t="inlineStr">
+      <c r="AR140" s="3" t="inlineStr">
         <is>
           <t>your workwear and military surplus range, including Carhartt</t>
         </is>
@@ -26873,26 +27573,31 @@
           <t>Missing Contact; Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL141" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM141" s="3" t="inlineStr">
+      <c r="AL141" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM141" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN141" s="3" t="inlineStr">
         <is>
           <t>Cold</t>
         </is>
       </c>
-      <c r="AN141" s="3" t="n"/>
-      <c r="AO141" s="4" t="inlineStr">
+      <c r="AO141" s="3" t="n"/>
+      <c r="AP141" s="4" t="inlineStr">
         <is>
           <t>Hi there, I came across your shop and noticed selling through Depop. I work with Fleek, a wholesale marketplace connecting retailers and resellers with inventory from trusted suppliers and brands. Would it be useful to see what's currently available that fits what you stock?</t>
         </is>
       </c>
-      <c r="AP141" s="4" t="inlineStr">
+      <c r="AQ141" s="4" t="inlineStr">
         <is>
           <t>Stage identified as New Lead (Cold). Personalisation drawn from channel (notes unavailable): selling through Depop. No prior contact on record - treated as first outreach.</t>
         </is>
       </c>
-      <c r="AQ141" s="3" t="inlineStr">
+      <c r="AR141" s="3" t="inlineStr">
         <is>
           <t>selling through Depop</t>
         </is>
@@ -27062,26 +27767,31 @@
           <t>Missing Instagram; Non-UK</t>
         </is>
       </c>
-      <c r="AL142" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM142" s="3" t="inlineStr">
+      <c r="AL142" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM142" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN142" s="3" t="inlineStr">
         <is>
           <t>Churned-Win-Back</t>
         </is>
       </c>
-      <c r="AN142" s="3" t="n"/>
-      <c r="AO142" s="4" t="inlineStr">
+      <c r="AO142" s="3" t="n"/>
+      <c r="AP142" s="4" t="inlineStr">
         <is>
           <t>Hi there, it's been a while since we last worked together, so wanted to reach out honestly rather than pretend nothing's changed. Given the reworked, archive-designer side of what you stock, I understand if the timing wasn't right before. Happy to work around your weekend trade - midweek suits us fine. Would it be worth a low-pressure conversation about what's changed on our side, in case it's relevant again?</t>
         </is>
       </c>
-      <c r="AP142" s="4" t="inlineStr">
+      <c r="AQ142" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Lapsed (Churned-Win-Back). Personalisation drawn from notes: your reworked and archive designer pieces. Notes flagged a specific objection/context, addressed directly rather than ignored. Last contacted 62 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ142" s="3" t="inlineStr">
+      <c r="AR142" s="3" t="inlineStr">
         <is>
           <t>your reworked and archive designer pieces</t>
         </is>
@@ -27251,26 +27961,31 @@
           <t>Missing Website</t>
         </is>
       </c>
-      <c r="AL143" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM143" s="3" t="inlineStr">
+      <c r="AL143" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM143" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN143" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN143" s="3" t="n"/>
-      <c r="AO143" s="4" t="inlineStr">
+      <c r="AO143" s="3" t="n"/>
+      <c r="AP143" s="4" t="inlineStr">
         <is>
           <t>Hi there, it's been a little while, so wanted to check back in given your retro football shirt and vintage sportswear range. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP143" s="4" t="inlineStr">
+      <c r="AQ143" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Negotiating (Re-Engagement). Personalisation drawn from notes: your retro football shirt and vintage sportswear range. Last contacted 46 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ143" s="3" t="inlineStr">
+      <c r="AR143" s="3" t="inlineStr">
         <is>
           <t>your retro football shirt and vintage sportswear range</t>
         </is>
@@ -27440,26 +28155,31 @@
           <t>None</t>
         </is>
       </c>
-      <c r="AL144" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM144" s="3" t="inlineStr">
+      <c r="AL144" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM144" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN144" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN144" s="3" t="n"/>
-      <c r="AO144" s="4" t="inlineStr">
+      <c r="AO144" s="3" t="n"/>
+      <c r="AP144" s="4" t="inlineStr">
         <is>
           <t>Hi Mila, it's been a little while, so wanted to check back in given your workwear and military surplus range, including Carhartt. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP144" s="4" t="inlineStr">
+      <c r="AQ144" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Meeting Booked (Re-Engagement). Personalisation drawn from notes: your workwear and military surplus range, including Carhartt. Last contacted 132 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ144" s="3" t="inlineStr">
+      <c r="AR144" s="3" t="inlineStr">
         <is>
           <t>your workwear and military surplus range, including Carhartt</t>
         </is>
@@ -27629,26 +28349,31 @@
           <t>Missing Contact; Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL145" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM145" s="3" t="inlineStr">
+      <c r="AL145" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM145" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN145" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN145" s="3" t="n"/>
-      <c r="AO145" s="4" t="inlineStr">
+      <c r="AO145" s="3" t="n"/>
+      <c r="AP145" s="4" t="inlineStr">
         <is>
           <t>Hi there, it's been a little while, so wanted to check back in given your live-sale presence on Whatnot. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP145" s="4" t="inlineStr">
+      <c r="AQ145" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Replied (Re-Engagement). Personalisation drawn from channel (notes unavailable): your live-sale presence on Whatnot. Last contacted 86 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ145" s="3" t="inlineStr">
+      <c r="AR145" s="3" t="inlineStr">
         <is>
           <t>your live-sale presence on Whatnot</t>
         </is>
@@ -27818,26 +28543,31 @@
           <t>None</t>
         </is>
       </c>
-      <c r="AL146" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM146" s="3" t="inlineStr">
+      <c r="AL146" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM146" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN146" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN146" s="3" t="n"/>
-      <c r="AO146" s="4" t="inlineStr">
+      <c r="AO146" s="3" t="n"/>
+      <c r="AP146" s="4" t="inlineStr">
         <is>
           <t>Hi Oscar, it's been a little while, so wanted to check back in given your workwear and military surplus range, including Carhartt. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Good to put a name to the shop after meeting at the market - still keen to swing by. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP146" s="4" t="inlineStr">
+      <c r="AQ146" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Visiting (Re-Engagement). Personalisation drawn from notes: your workwear and military surplus range, including Carhartt. Notes flagged a specific objection/context, addressed directly rather than ignored. Last contacted 43 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ146" s="3" t="inlineStr">
+      <c r="AR146" s="3" t="inlineStr">
         <is>
           <t>your workwear and military surplus range, including Carhartt</t>
         </is>
@@ -28007,26 +28737,31 @@
           <t>None</t>
         </is>
       </c>
-      <c r="AL147" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM147" s="3" t="inlineStr">
+      <c r="AL147" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM147" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN147" s="3" t="inlineStr">
         <is>
           <t>Cold</t>
         </is>
       </c>
-      <c r="AN147" s="3" t="n"/>
-      <c r="AO147" s="4" t="inlineStr">
+      <c r="AO147" s="3" t="n"/>
+      <c r="AP147" s="4" t="inlineStr">
         <is>
           <t>Hi there, I came across your shop and noticed your retro football shirt and vintage sportswear range. I work with Fleek, a wholesale marketplace connecting retailers and resellers with inventory from trusted suppliers and brands. Happy to work around your weekend trade - midweek suits us fine. Would it be useful to see what's currently available that fits what you stock?</t>
         </is>
       </c>
-      <c r="AP147" s="4" t="inlineStr">
+      <c r="AQ147" s="4" t="inlineStr">
         <is>
           <t>Stage identified as New Lead (Cold). Personalisation drawn from notes: your retro football shirt and vintage sportswear range. Notes flagged a specific objection/context, addressed directly rather than ignored. No prior contact on record - treated as first outreach.</t>
         </is>
       </c>
-      <c r="AQ147" s="3" t="inlineStr">
+      <c r="AR147" s="3" t="inlineStr">
         <is>
           <t>your retro football shirt and vintage sportswear range</t>
         </is>
@@ -28196,26 +28931,31 @@
           <t>Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL148" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM148" s="3" t="inlineStr">
+      <c r="AL148" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM148" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN148" s="3" t="inlineStr">
         <is>
           <t>Inbound</t>
         </is>
       </c>
-      <c r="AN148" s="3" t="n"/>
-      <c r="AO148" s="4" t="inlineStr">
+      <c r="AO148" s="3" t="n"/>
+      <c r="AP148" s="4" t="inlineStr">
         <is>
           <t>Hi there, thanks for getting in touch - I had a look at running your shop straight through Instagram DMs before writing back. Fleek connects shops like yours with inventory from trusted suppliers, so given the DM-led way you run sales, it seemed worth a proper reply rather than a generic one. What's the main gap in sourcing right now - more volume, more variety, or something specific you're struggling to find?</t>
         </is>
       </c>
-      <c r="AP148" s="4" t="inlineStr">
+      <c r="AQ148" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Inbound (Inbound). Personalisation drawn from notes: running your shop straight through Instagram DMs. No prior contact on record - treated as first outreach.</t>
         </is>
       </c>
-      <c r="AQ148" s="3" t="inlineStr">
+      <c r="AR148" s="3" t="inlineStr">
         <is>
           <t>running your shop straight through Instagram DMs</t>
         </is>
@@ -28385,26 +29125,31 @@
           <t>None</t>
         </is>
       </c>
-      <c r="AL149" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM149" s="3" t="inlineStr">
+      <c r="AL149" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM149" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN149" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN149" s="3" t="n"/>
-      <c r="AO149" s="4" t="inlineStr">
+      <c r="AO149" s="3" t="n"/>
+      <c r="AP149" s="4" t="inlineStr">
         <is>
           <t>Hi Sofia, it's been a little while, so wanted to check back in given your 80s/90s denim and sportswear edit. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick correction on that: we work with shops at a range of sizes, not just small resellers - happy to show you what that actually looks like. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP149" s="4" t="inlineStr">
+      <c r="AQ149" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Quote Sent (Re-Engagement). Personalisation drawn from notes: your 80s/90s denim and sportswear edit. Notes flagged a specific objection/context, addressed directly rather than ignored. Last contacted 27 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ149" s="3" t="inlineStr">
+      <c r="AR149" s="3" t="inlineStr">
         <is>
           <t>your 80s/90s denim and sportswear edit</t>
         </is>
@@ -28574,26 +29319,31 @@
           <t>None</t>
         </is>
       </c>
-      <c r="AL150" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM150" s="3" t="inlineStr">
+      <c r="AL150" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM150" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN150" s="3" t="inlineStr">
         <is>
           <t>Inbound</t>
         </is>
       </c>
-      <c r="AN150" s="3" t="n"/>
-      <c r="AO150" s="4" t="inlineStr">
+      <c r="AO150" s="3" t="n"/>
+      <c r="AP150" s="4" t="inlineStr">
         <is>
           <t>Hi Rosa, thanks for getting in touch - I had a look at your curated womenswear built around Levi's and band tees before writing back. Fleek connects shops like yours with inventory from trusted suppliers, so given the Levi's and band-tee-led womenswear edit you're known for, it seemed worth a proper reply rather than a generic one. What's the main gap in sourcing right now - more volume, more variety, or something specific you're struggling to find?</t>
         </is>
       </c>
-      <c r="AP150" s="4" t="inlineStr">
+      <c r="AQ150" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Inbound (Inbound). Personalisation drawn from notes: your curated womenswear built around Levi's and band tees. No prior contact on record - treated as first outreach.</t>
         </is>
       </c>
-      <c r="AQ150" s="3" t="inlineStr">
+      <c r="AR150" s="3" t="inlineStr">
         <is>
           <t>your curated womenswear built around Levi's and band tees</t>
         </is>
@@ -28763,27 +29513,32 @@
           <t>Non-UK</t>
         </is>
       </c>
-      <c r="AL151" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM151" s="3" t="inlineStr">
+      <c r="AL151" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM151" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN151" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN151" s="3" t="n"/>
-      <c r="AO151" s="4" t="inlineStr">
+      <c r="AO151" s="3" t="n"/>
+      <c r="AP151" s="4" t="inlineStr">
         <is>
           <t>English: Hi Oscar, it's been a little while, so wanted to check back in given your Y2K, grunge and reworked one-off pieces. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?
 Translated (French): Bonjour Oscar, cela fait un moment, je voulais donc reprendre contact étant donné vos pièces Y2K, grunge et retravaillées en pièce unique. Aucune pression si le moment n'est plus idéal, mais si l'approvisionnement reste d'actualité, je serais ravi d'en reparler. Cela vaudrait-il la peine d'en discuter rapidement ?</t>
         </is>
       </c>
-      <c r="AP151" s="4" t="inlineStr">
+      <c r="AQ151" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Contacted (Re-Engagement). Personalisation drawn from notes: your Y2K, grunge and reworked one-off pieces. Last contacted 76 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ151" s="3" t="inlineStr">
+      <c r="AR151" s="3" t="inlineStr">
         <is>
           <t>your Y2K, grunge and reworked one-off pieces</t>
         </is>
@@ -28953,27 +29708,32 @@
           <t>Non-UK</t>
         </is>
       </c>
-      <c r="AL152" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM152" s="3" t="inlineStr">
+      <c r="AL152" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM152" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN152" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN152" s="3" t="n"/>
-      <c r="AO152" s="4" t="inlineStr">
+      <c r="AO152" s="3" t="n"/>
+      <c r="AP152" s="4" t="inlineStr">
         <is>
           <t>English: Hi there, it's been a little while, so wanted to check back in given your Y2K, grunge and reworked one-off pieces. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Fair to compare - happy to let the numbers speak for themselves rather than argue the case. Worth a quick chat to see where things stand?
 Translated (Dutch): Hallo, het is alweer even geleden, dus ik wilde graag opnieuw contact opnemen gezien uw Y2K-, grunge- en bewerkte unieke stukken. Geen druk als de timing is veranderd, maar als inkoop nog steeds relevant voor u is, denk ik graag weer mee. Het is logisch om te vergelijken - ik laat de cijfers liever voor zichzelf spreken dan dat ik erover in discussie ga. Zou een kort gesprek de moeite waard zijn?</t>
         </is>
       </c>
-      <c r="AP152" s="4" t="inlineStr">
+      <c r="AQ152" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Replied (Re-Engagement). Personalisation drawn from notes: your Y2K, grunge and reworked one-off pieces. Notes flagged a specific objection/context, addressed directly rather than ignored. Last contacted 87 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ152" s="3" t="inlineStr">
+      <c r="AR152" s="3" t="inlineStr">
         <is>
           <t>your Y2K, grunge and reworked one-off pieces</t>
         </is>
@@ -29143,26 +29903,31 @@
           <t>Missing Contact; Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL153" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM153" s="3" t="inlineStr">
+      <c r="AL153" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM153" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN153" s="3" t="inlineStr">
         <is>
           <t>Customer Check-In</t>
         </is>
       </c>
-      <c r="AN153" s="3" t="n"/>
-      <c r="AO153" s="4" t="inlineStr">
+      <c r="AO153" s="3" t="n"/>
+      <c r="AP153" s="4" t="inlineStr">
         <is>
           <t>Hi there, wanted to check in properly rather than send a generic update, given your presence across both Depop and Vinted. Keen to hear how things have been going and whether there's anything new worth exploring together. Any gaps in what you're sourcing at the moment, or new ranges you're thinking about?</t>
         </is>
       </c>
-      <c r="AP153" s="4" t="inlineStr">
+      <c r="AQ153" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Closed Won (Customer Check-In). Personalisation drawn from notes: selling across both Depop and Vinted. Last contacted 36 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ153" s="3" t="inlineStr">
+      <c r="AR153" s="3" t="inlineStr">
         <is>
           <t>selling across both Depop and Vinted</t>
         </is>
@@ -29332,26 +30097,31 @@
           <t>Missing Contact; Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL154" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM154" s="3" t="inlineStr">
+      <c r="AL154" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM154" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN154" s="3" t="inlineStr">
         <is>
           <t>Cold</t>
         </is>
       </c>
-      <c r="AN154" s="3" t="n"/>
-      <c r="AO154" s="4" t="inlineStr">
+      <c r="AO154" s="3" t="n"/>
+      <c r="AP154" s="4" t="inlineStr">
         <is>
           <t>Hi there, I came across your shop and noticed running sales through Instagram. I work with Fleek, a wholesale marketplace connecting retailers and resellers with inventory from trusted suppliers and brands. Would it be useful to see what's currently available that fits what you stock?</t>
         </is>
       </c>
-      <c r="AP154" s="4" t="inlineStr">
+      <c r="AQ154" s="4" t="inlineStr">
         <is>
           <t>Stage identified as New Lead (Cold). Personalisation drawn from channel (notes unavailable): running sales through Instagram. No prior contact on record - treated as first outreach.</t>
         </is>
       </c>
-      <c r="AQ154" s="3" t="inlineStr">
+      <c r="AR154" s="3" t="inlineStr">
         <is>
           <t>running sales through Instagram</t>
         </is>
@@ -29521,27 +30291,32 @@
           <t>Non-UK</t>
         </is>
       </c>
-      <c r="AL155" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM155" s="3" t="inlineStr">
+      <c r="AL155" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM155" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN155" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN155" s="3" t="n"/>
-      <c r="AO155" s="4" t="inlineStr">
+      <c r="AO155" s="3" t="n"/>
+      <c r="AP155" s="4" t="inlineStr">
         <is>
           <t>English: Hi there, it's been a little while, so wanted to check back in given your retro football shirt and vintage sportswear range. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?
 Translated (German): Hallo, es ist eine Weile her, deshalb wollte ich mich angesichts Ihr Sortiment an Retro-Fußballtrikots und Vintage-Sportbekleidung noch einmal melden. Kein Druck, falls sich der Zeitpunkt geändert hat, aber falls Beschaffung weiterhin ein Thema für Sie ist, spreche ich gerne wieder darüber. Würde sich ein kurzes Gespräch lohnen?</t>
         </is>
       </c>
-      <c r="AP155" s="4" t="inlineStr">
+      <c r="AQ155" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Contacted (Re-Engagement). Personalisation drawn from notes: your retro football shirt and vintage sportswear range. Last contacted 84 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ155" s="3" t="inlineStr">
+      <c r="AR155" s="3" t="inlineStr">
         <is>
           <t>your retro football shirt and vintage sportswear range</t>
         </is>
@@ -29711,26 +30486,31 @@
           <t>None</t>
         </is>
       </c>
-      <c r="AL156" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM156" s="3" t="inlineStr">
+      <c r="AL156" s="3" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="AM156" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN156" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN156" s="3" t="n"/>
-      <c r="AO156" s="4" t="inlineStr">
+      <c r="AO156" s="3" t="n"/>
+      <c r="AP156" s="4" t="inlineStr">
         <is>
           <t>Hi there, it's been a little while, so wanted to check back in given your curated womenswear built around Levi's and band tees. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP156" s="4" t="inlineStr">
+      <c r="AQ156" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Meeting Booked (Re-Engagement). Personalisation drawn from notes: your curated womenswear built around Levi's and band tees. Last contacted 62 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ156" s="3" t="inlineStr">
+      <c r="AR156" s="3" t="inlineStr">
         <is>
           <t>your curated womenswear built around Levi's and band tees</t>
         </is>
@@ -29900,27 +30680,32 @@
           <t>Missing Website; Non-UK</t>
         </is>
       </c>
-      <c r="AL157" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM157" s="3" t="inlineStr">
+      <c r="AL157" s="3" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="AM157" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN157" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN157" s="3" t="n"/>
-      <c r="AO157" s="4" t="inlineStr">
+      <c r="AO157" s="3" t="n"/>
+      <c r="AP157" s="4" t="inlineStr">
         <is>
           <t>English: Hi there, it's been a little while, so wanted to check back in given your streetwear edit built around Nike, Adidas and Ralph Lauren. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?
 Translated (French): Bonjour, cela fait un moment, je voulais donc reprendre contact étant donné votre sélection streetwear construite autour de Nike, Adidas et Ralph Lauren. Aucune pression si le moment n'est plus idéal, mais si l'approvisionnement reste d'actualité, je serais ravi d'en reparler. Cela vaudrait-il la peine d'en discuter rapidement ?</t>
         </is>
       </c>
-      <c r="AP157" s="4" t="inlineStr">
+      <c r="AQ157" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Visit Booked (Re-Engagement). Personalisation drawn from notes: your streetwear edit built around Nike, Adidas and Ralph Lauren. Last contacted 41 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ157" s="3" t="inlineStr">
+      <c r="AR157" s="3" t="inlineStr">
         <is>
           <t>your streetwear edit built around Nike, Adidas and Ralph Lauren</t>
         </is>
@@ -30090,26 +30875,31 @@
           <t>Missing Contact; Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL158" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM158" s="3" t="inlineStr">
+      <c r="AL158" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM158" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN158" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN158" s="3" t="n"/>
-      <c r="AO158" s="4" t="inlineStr">
+      <c r="AO158" s="3" t="n"/>
+      <c r="AP158" s="4" t="inlineStr">
         <is>
           <t>Hi there, it's been a little while, so wanted to check back in given your live-sale format on Whatnot. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP158" s="4" t="inlineStr">
+      <c r="AQ158" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Contacted (Re-Engagement). Personalisation drawn from notes: your live-sale format on Whatnot. Last contacted 84 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ158" s="3" t="inlineStr">
+      <c r="AR158" s="3" t="inlineStr">
         <is>
           <t>your live-sale format on Whatnot</t>
         </is>
@@ -30279,26 +31069,31 @@
           <t>Missing Contact; Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL159" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM159" s="3" t="inlineStr">
+      <c r="AL159" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM159" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN159" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN159" s="3" t="n"/>
-      <c r="AO159" s="4" t="inlineStr">
+      <c r="AO159" s="3" t="n"/>
+      <c r="AP159" s="4" t="inlineStr">
         <is>
           <t>Hi there, it's been a little while, so wanted to check back in given selling across both Depop and Vinted. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP159" s="4" t="inlineStr">
+      <c r="AQ159" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Quote Sent (Re-Engagement). Personalisation drawn from notes: selling across both Depop and Vinted. Last contacted 86 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ159" s="3" t="inlineStr">
+      <c r="AR159" s="3" t="inlineStr">
         <is>
           <t>selling across both Depop and Vinted</t>
         </is>
@@ -30468,26 +31263,31 @@
           <t>Missing Contact; Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL160" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM160" s="3" t="inlineStr">
+      <c r="AL160" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM160" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN160" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN160" s="3" t="n"/>
-      <c r="AO160" s="4" t="inlineStr">
+      <c r="AO160" s="3" t="n"/>
+      <c r="AP160" s="4" t="inlineStr">
         <is>
           <t>Hi there, it's been a little while, so wanted to check back in given how quickly your stock turns over. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP160" s="4" t="inlineStr">
+      <c r="AQ160" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Contacted (Re-Engagement). Personalisation drawn from notes: how quickly your stock turns over. Last contacted 37 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ160" s="3" t="inlineStr">
+      <c r="AR160" s="3" t="inlineStr">
         <is>
           <t>how quickly your stock turns over</t>
         </is>
@@ -30657,26 +31457,31 @@
           <t>Missing Website</t>
         </is>
       </c>
-      <c r="AL161" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM161" s="3" t="inlineStr">
+      <c r="AL161" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM161" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN161" s="3" t="inlineStr">
         <is>
           <t>Re-Engagement</t>
         </is>
       </c>
-      <c r="AN161" s="3" t="n"/>
-      <c r="AO161" s="4" t="inlineStr">
+      <c r="AO161" s="3" t="n"/>
+      <c r="AP161" s="4" t="inlineStr">
         <is>
           <t>Hi there, it's been a little while, so wanted to check back in given your Y2K, grunge and reworked one-off pieces. No pressure if the timing's shifted, but if sourcing is still on your radar, happy to pick things back up. Worth a quick chat to see where things stand?</t>
         </is>
       </c>
-      <c r="AP161" s="4" t="inlineStr">
+      <c r="AQ161" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Replied (Re-Engagement). Personalisation drawn from notes: your Y2K, grunge and reworked one-off pieces. Last contacted 86 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ161" s="3" t="inlineStr">
+      <c r="AR161" s="3" t="inlineStr">
         <is>
           <t>your Y2K, grunge and reworked one-off pieces</t>
         </is>
@@ -30846,26 +31651,31 @@
           <t>Missing Contact; Missing Website; Unverified Location</t>
         </is>
       </c>
-      <c r="AL162" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM162" s="3" t="inlineStr">
+      <c r="AL162" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM162" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN162" s="3" t="inlineStr">
         <is>
           <t>Cold</t>
         </is>
       </c>
-      <c r="AN162" s="3" t="n"/>
-      <c r="AO162" s="4" t="inlineStr">
+      <c r="AO162" s="3" t="n"/>
+      <c r="AP162" s="4" t="inlineStr">
         <is>
           <t>Hi there, I came across your shop and noticed your live-sale format on Whatnot. I work with Fleek, a wholesale marketplace connecting retailers and resellers with inventory from trusted suppliers and brands. Would it be useful to see what's currently available that fits what you stock?</t>
         </is>
       </c>
-      <c r="AP162" s="4" t="inlineStr">
+      <c r="AQ162" s="4" t="inlineStr">
         <is>
           <t>Stage identified as New Lead (Cold). Personalisation drawn from notes: your live-sale format on Whatnot. No prior contact on record - treated as first outreach.</t>
         </is>
       </c>
-      <c r="AQ162" s="3" t="inlineStr">
+      <c r="AR162" s="3" t="inlineStr">
         <is>
           <t>your live-sale format on Whatnot</t>
         </is>
@@ -31035,26 +31845,31 @@
           <t>None</t>
         </is>
       </c>
-      <c r="AL163" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM163" s="3" t="inlineStr">
+      <c r="AL163" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM163" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN163" s="3" t="inlineStr">
         <is>
           <t>Cold</t>
         </is>
       </c>
-      <c r="AN163" s="3" t="n"/>
-      <c r="AO163" s="4" t="inlineStr">
+      <c r="AO163" s="3" t="n"/>
+      <c r="AP163" s="4" t="inlineStr">
         <is>
           <t>Hi there, I came across your shop and noticed your streetwear edit built around Nike, Adidas and Ralph Lauren. I work with Fleek, a wholesale marketplace connecting retailers and resellers with inventory from trusted suppliers and brands. Would it be useful to see what's currently available that fits what you stock?</t>
         </is>
       </c>
-      <c r="AP163" s="4" t="inlineStr">
+      <c r="AQ163" s="4" t="inlineStr">
         <is>
           <t>Stage identified as New Lead (Cold). Personalisation drawn from notes: your streetwear edit built around Nike, Adidas and Ralph Lauren. No prior contact on record - treated as first outreach.</t>
         </is>
       </c>
-      <c r="AQ163" s="3" t="inlineStr">
+      <c r="AR163" s="3" t="inlineStr">
         <is>
           <t>your streetwear edit built around Nike, Adidas and Ralph Lauren</t>
         </is>
@@ -31224,26 +32039,31 @@
           <t>Missing Website; Missing Instagram</t>
         </is>
       </c>
-      <c r="AL164" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM164" s="3" t="inlineStr">
+      <c r="AL164" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="AM164" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN164" s="3" t="inlineStr">
         <is>
           <t>Inbound</t>
         </is>
       </c>
-      <c r="AN164" s="3" t="n"/>
-      <c r="AO164" s="4" t="inlineStr">
+      <c r="AO164" s="3" t="n"/>
+      <c r="AP164" s="4" t="inlineStr">
         <is>
           <t>Hi Grace, thanks for getting in touch - I had a look at your curated womenswear built around Levi's and band tees before writing back. Fleek connects shops like yours with inventory from trusted suppliers, so given the Levi's and band-tee-led womenswear edit you're known for, it seemed worth a proper reply rather than a generic one. What's the main gap in sourcing right now - more volume, more variety, or something specific you're struggling to find?</t>
         </is>
       </c>
-      <c r="AP164" s="4" t="inlineStr">
+      <c r="AQ164" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Inbound (Inbound). Personalisation drawn from notes: your curated womenswear built around Levi's and band tees. No prior contact on record - treated as first outreach.</t>
         </is>
       </c>
-      <c r="AQ164" s="3" t="inlineStr">
+      <c r="AR164" s="3" t="inlineStr">
         <is>
           <t>your curated womenswear built around Levi's and band tees</t>
         </is>
@@ -31413,26 +32233,31 @@
           <t>None</t>
         </is>
       </c>
-      <c r="AL165" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM165" s="3" t="inlineStr">
+      <c r="AL165" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM165" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN165" s="3" t="inlineStr">
         <is>
           <t>Inbound</t>
         </is>
       </c>
-      <c r="AN165" s="3" t="n"/>
-      <c r="AO165" s="4" t="inlineStr">
+      <c r="AO165" s="3" t="n"/>
+      <c r="AP165" s="4" t="inlineStr">
         <is>
           <t>Hi Rosa, thanks for getting in touch - I had a look at your streetwear edit built around Nike, Adidas and Ralph Lauren before writing back. Fleek connects shops like yours with inventory from trusted suppliers, so given the Nike/Adidas/Ralph Lauren streetwear edit you carry, it seemed worth a proper reply rather than a generic one. What's the main gap in sourcing right now - more volume, more variety, or something specific you're struggling to find?</t>
         </is>
       </c>
-      <c r="AP165" s="4" t="inlineStr">
+      <c r="AQ165" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Inbound (Inbound). Personalisation drawn from notes: your streetwear edit built around Nike, Adidas and Ralph Lauren. No prior contact on record - treated as first outreach.</t>
         </is>
       </c>
-      <c r="AQ165" s="3" t="inlineStr">
+      <c r="AR165" s="3" t="inlineStr">
         <is>
           <t>your streetwear edit built around Nike, Adidas and Ralph Lauren</t>
         </is>
@@ -31602,33 +32427,38 @@
           <t>Missing Website; Missing Instagram</t>
         </is>
       </c>
-      <c r="AL166" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM166" s="3" t="inlineStr">
+      <c r="AL166" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="AM166" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN166" s="3" t="inlineStr">
         <is>
           <t>Cold</t>
         </is>
       </c>
-      <c r="AN166" s="3" t="n"/>
-      <c r="AO166" s="4" t="inlineStr">
+      <c r="AO166" s="3" t="n"/>
+      <c r="AP166" s="4" t="inlineStr">
         <is>
           <t>Hi Ellie, I came across your shop and noticed your workwear and military surplus range, including Carhartt. I work with Fleek, a wholesale marketplace connecting retailers and resellers with inventory from trusted suppliers and brands. Good to put a name to the shop after meeting at the market - still keen to swing by. Would it be useful to see what's currently available that fits what you stock?</t>
         </is>
       </c>
-      <c r="AP166" s="4" t="inlineStr">
+      <c r="AQ166" s="4" t="inlineStr">
         <is>
           <t>Stage identified as Contacted (Cold). Personalisation drawn from notes: your workwear and military surplus range, including Carhartt. Notes flagged a specific objection/context, addressed directly rather than ignored. Last contacted 28 day(s) ago - timing supports a follow-up now.</t>
         </is>
       </c>
-      <c r="AQ166" s="3" t="inlineStr">
+      <c r="AR166" s="3" t="inlineStr">
         <is>
           <t>your workwear and military surplus range, including Carhartt</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AQ166"/>
+  <autoFilter ref="A2:AR166"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -31639,7 +32469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK25"/>
+  <dimension ref="A1:AL25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -31679,6 +32509,7 @@
     <col width="40" customWidth="1" min="35" max="35"/>
     <col width="22" customWidth="1" min="36" max="36"/>
     <col width="19" customWidth="1" min="37" max="37"/>
+    <col width="12" customWidth="1" min="38" max="38"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -31867,6 +32698,11 @@
           <t>data_quality_flag</t>
         </is>
       </c>
+      <c r="AL1" s="2" t="inlineStr">
+        <is>
+          <t>spend_tier</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -32032,6 +32868,11 @@
           <t>Possible Duplicate - Unverified</t>
         </is>
       </c>
+      <c r="AL2" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -32197,6 +33038,11 @@
           <t>Missing Website</t>
         </is>
       </c>
+      <c r="AL3" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -32362,6 +33208,11 @@
           <t>Possible Duplicate - Unverified</t>
         </is>
       </c>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -32527,6 +33378,11 @@
           <t>Missing Contact; Missing Instagram; Non-UK</t>
         </is>
       </c>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -32692,6 +33548,11 @@
           <t>Missing Website; Possible Duplicate - Unverified</t>
         </is>
       </c>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -32857,6 +33718,11 @@
           <t>Missing Instagram; Non-UK</t>
         </is>
       </c>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -33022,6 +33888,11 @@
           <t>Missing Website; Missing Instagram; Non-UK; Possible Duplicate - Unverified</t>
         </is>
       </c>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -33187,6 +34058,11 @@
           <t>Missing Contact</t>
         </is>
       </c>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -33352,6 +34228,11 @@
           <t>Missing Website; Possible Duplicate - Unverified</t>
         </is>
       </c>
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -33517,6 +34398,11 @@
           <t>Non-UK; Possible Duplicate - Unverified</t>
         </is>
       </c>
+      <c r="AL11" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -33682,6 +34568,11 @@
           <t>Missing Website</t>
         </is>
       </c>
+      <c r="AL12" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -33847,6 +34738,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="AL13" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -34012,6 +34908,11 @@
           <t>Missing Website; Possible Duplicate - Unverified</t>
         </is>
       </c>
+      <c r="AL14" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -34177,6 +35078,11 @@
           <t>Missing Website; Missing Instagram</t>
         </is>
       </c>
+      <c r="AL15" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -34342,6 +35248,11 @@
           <t>Non-UK</t>
         </is>
       </c>
+      <c r="AL16" s="3" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -34507,6 +35418,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="AL17" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -34672,6 +35588,11 @@
           <t>Missing Instagram</t>
         </is>
       </c>
+      <c r="AL18" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -34837,6 +35758,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="AL19" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -35002,6 +35928,11 @@
           <t>Missing Website</t>
         </is>
       </c>
+      <c r="AL20" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -35167,6 +36098,11 @@
           <t>Missing Website</t>
         </is>
       </c>
+      <c r="AL21" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -35332,6 +36268,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="AL22" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -35497,6 +36438,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="AL23" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -35662,6 +36608,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="AL24" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -35827,9 +36778,14 @@
           <t>Missing Website</t>
         </is>
       </c>
+      <c r="AL25" s="3" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AK25"/>
+  <autoFilter ref="A1:AL25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -36238,11 +37194,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B78"/>
+  <dimension ref="A1:F98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -36942,6 +37902,346 @@
       </c>
       <c r="B78" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t>Leads by spend_tier (Tier 1: GBP5k+/mo, Tier 2: GBP2k-4,999/mo, Tier 3: under GBP2k/mo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="7" t="inlineStr">
+        <is>
+          <t>Lead count by city and spend_tier (sorted by total leads, descending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="8" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="B86" s="8" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="C86" s="8" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="D86" s="8" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="E86" s="8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F86" s="8" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>0</v>
+      </c>
+      <c r="C87" t="n">
+        <v>15</v>
+      </c>
+      <c r="D87" t="n">
+        <v>47</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>8</v>
+      </c>
+      <c r="C88" t="n">
+        <v>24</v>
+      </c>
+      <c r="D88" t="n">
+        <v>20</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Brighton</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>1</v>
+      </c>
+      <c r="C89" t="n">
+        <v>5</v>
+      </c>
+      <c r="D89" t="n">
+        <v>3</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>3</v>
+      </c>
+      <c r="C90" t="n">
+        <v>4</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Bristol</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>0</v>
+      </c>
+      <c r="C91" t="n">
+        <v>4</v>
+      </c>
+      <c r="D91" t="n">
+        <v>2</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>0</v>
+      </c>
+      <c r="C92" t="n">
+        <v>3</v>
+      </c>
+      <c r="D92" t="n">
+        <v>2</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>2</v>
+      </c>
+      <c r="C93" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" t="n">
+        <v>3</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>0</v>
+      </c>
+      <c r="C94" t="n">
+        <v>3</v>
+      </c>
+      <c r="D94" t="n">
+        <v>1</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>0</v>
+      </c>
+      <c r="C95" t="n">
+        <v>2</v>
+      </c>
+      <c r="D95" t="n">
+        <v>2</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>2</v>
+      </c>
+      <c r="C96" t="n">
+        <v>2</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>0</v>
+      </c>
+      <c r="C97" t="n">
+        <v>3</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Leeds</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>0</v>
+      </c>
+      <c r="C98" t="n">
+        <v>0</v>
+      </c>
+      <c r="D98" t="n">
+        <v>3</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/output/crm_with_outreach.xlsx
+++ b/output/crm_with_outreach.xlsx
@@ -11,10 +11,12 @@
     <sheet name="Disqualified Leads" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Cleaning Log" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Channel &amp; CRM Summary" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="City Prioritisation" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cleaned Dataset'!$A$2:$AR$166</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Disqualified Leads'!$A$1:$AL$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'City Prioritisation'!$A$2:$L$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -38247,4 +38249,564 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Ranked by priority_score (density 25% + spend potential 35% + pipeline warmth 25% + win rate 15%, each normalised 0-1 across cities). priority_reasoning spells out the real numbers behind every score - never trust the score alone without reading it. Physical Store leads with a known city only; online resellers are reached by DM, not a city visit, and leads with no city can't inform this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>qualified_leads</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>total_monthly_spend_potential_gbp</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>avg_monthly_spend_gbp</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>warm_leads</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>warm_ratio</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>won_customers</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>lost_or_churned</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>win_rate</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>priority_score</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>priority_rank</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>priority_reasoning</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>157673</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>3032</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>52 qualified physical-store leads (#1 of 11 by density); an estimated £157,673/month combined spend potential (#1 of 11); 37% of the pipeline already warm (Engaged/Opportunity) (#7 of 11); a 18% win rate (2 won vs 9 lost/churned).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Brighton</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>22078</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>2453</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>9 qualified physical-store leads (#2 of 11 by density); an estimated £22,078/month combined spend potential (#3 of 11); 67% of the pipeline already warm (Engaged/Opportunity) (#1 of 11); no won/lost history yet to judge receptiveness.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>11752</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>3917</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>3 qualified physical-store leads (#10 of 11 by density); an estimated £11,752/month combined spend potential (#7 of 11); 67% of the pipeline already warm (Engaged/Opportunity) (#1 of 11); no won/lost history yet to judge receptiveness.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>30547</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>4364</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>7 qualified physical-store leads (#3 of 11 by density); an estimated £30,547/month combined spend potential (#2 of 11); 43% of the pipeline already warm (Engaged/Opportunity) (#6 of 11); a 50% win rate (1 won vs 1 lost/churned) - small sample, treat as directional only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Leeds</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>3778</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>1259</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>3 qualified physical-store leads (#10 of 11 by density); an estimated £3,778/month combined spend potential (#11 of 11); 67% of the pipeline already warm (Engaged/Opportunity) (#1 of 11); no won/lost history yet to judge receptiveness.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>20889</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>5222</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>4 qualified physical-store leads (#7 of 11 by density); an estimated £20,889/month combined spend potential (#4 of 11); 50% of the pipeline already warm (Engaged/Opportunity) (#4 of 11); no won/lost history yet to judge receptiveness.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>9395</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>2349</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>4 qualified physical-store leads (#7 of 11 by density); an estimated £9,395/month combined spend potential (#10 of 11); 25% of the pipeline already warm (Engaged/Opportunity) (#9 of 11); a 100% win rate (1 won vs 0 lost/churned) - small sample, treat as directional only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>9874</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>2468</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>4 qualified physical-store leads (#7 of 11 by density); an estimated £9,874/month combined spend potential (#9 of 11); 50% of the pipeline already warm (Engaged/Opportunity) (#4 of 11); no won/lost history yet to judge receptiveness.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Bristol</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>13369</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>2228</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>6 qualified physical-store leads (#4 of 11 by density); an estimated £13,369/month combined spend potential (#6 of 11); 33% of the pipeline already warm (Engaged/Opportunity) (#8 of 11); a 0% win rate (0 won vs 1 lost/churned) - small sample, treat as directional only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>13421</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>2684</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>5 qualified physical-store leads (#5 of 11 by density); an estimated £13,421/month combined spend potential (#5 of 11); 20% of the pipeline already warm (Engaged/Opportunity) (#10 of 11); a 0% win rate (0 won vs 2 lost/churned) - small sample, treat as directional only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>11027</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>2205</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>5 qualified physical-store leads (#5 of 11 by density); an estimated £11,027/month combined spend potential (#8 of 11); 0% of the pipeline already warm (Engaged/Opportunity) (#11 of 11); no won/lost history yet to judge receptiveness.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:L13"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>